--- a/dados.xlsx
+++ b/dados.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://concresupersc-my.sharepoint.com/personal/marketing_concresupersc_onmicrosoft_com/Documents/Área de Trabalho/C.I.V/Dashbord/DASHBOARD-METAS-PROPOSTAS/Teste 02 mudança/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://concresupersc-my.sharepoint.com/personal/marketing_concresupersc_onmicrosoft_com/Documents/Área de Trabalho/C.I.V/Dashbord/DASHBOARD-METAS-PROPOSTAS/Teste 06 mudança/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="533" documentId="8_{A291900F-2FC4-4CBC-95EF-8FF0E06A2678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FF61C591-361C-4166-B8F8-A9B92DBC2069}"/>
+  <xr:revisionPtr revIDLastSave="548" documentId="8_{A291900F-2FC4-4CBC-95EF-8FF0E06A2678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DAAED4D7-20E2-4153-8142-ADD706916AE5}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="34785" yWindow="-3135" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dados Diários" sheetId="1" r:id="rId1"/>
@@ -11265,7 +11265,7 @@
         <v>6</v>
       </c>
       <c r="D2" s="18">
-        <v>4117</v>
+        <v>4284</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
@@ -11342,7 +11342,7 @@
         <v>6</v>
       </c>
       <c r="D8" s="18">
-        <v>4178</v>
+        <v>3808</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11383,7 +11383,7 @@
       </c>
       <c r="D11" s="17"/>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
         <v>21</v>
       </c>
@@ -11395,7 +11395,7 @@
       </c>
       <c r="D12" s="18"/>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
         <v>22</v>
       </c>
@@ -11418,7 +11418,7 @@
         <v>6</v>
       </c>
       <c r="D14" s="18">
-        <v>1336.5</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
@@ -11494,7 +11494,7 @@
         <v>11</v>
       </c>
       <c r="D20" s="18">
-        <v>3131.5</v>
+        <v>4290</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -11570,7 +11570,7 @@
         <v>11</v>
       </c>
       <c r="D26" s="18">
-        <v>2671</v>
+        <v>2860</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -11646,7 +11646,7 @@
         <v>24</v>
       </c>
       <c r="D32" s="18">
-        <v>1554.5</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -11722,7 +11722,7 @@
         <v>26</v>
       </c>
       <c r="D38" s="18">
-        <v>1564</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -11798,7 +11798,7 @@
         <v>28</v>
       </c>
       <c r="D44" s="18">
-        <v>955</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -11874,7 +11874,7 @@
         <v>30</v>
       </c>
       <c r="D50" s="18">
-        <v>1665</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">

--- a/dados.xlsx
+++ b/dados.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://concresupersc-my.sharepoint.com/personal/marketing_concresupersc_onmicrosoft_com/Documents/Área de Trabalho/C.I.V/Dashbord/DASHBOARD-METAS-PROPOSTAS/Teste 06 mudança/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://concresupersc-my.sharepoint.com/personal/marketing_concresupersc_onmicrosoft_com/Documents/Área de Trabalho/C.I.V/Dashbord/DASHBOARD-METAS-PROPOSTAS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="548" documentId="8_{A291900F-2FC4-4CBC-95EF-8FF0E06A2678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DAAED4D7-20E2-4153-8142-ADD706916AE5}"/>
+  <xr:revisionPtr revIDLastSave="568" documentId="8_{A291900F-2FC4-4CBC-95EF-8FF0E06A2678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DC43AA1F-2E48-4B5D-9589-500C29BACCCA}"/>
   <bookViews>
-    <workbookView xWindow="34785" yWindow="-3135" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="34785" yWindow="-3135" windowWidth="14610" windowHeight="15585" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dados Diários" sheetId="1" r:id="rId1"/>
@@ -10100,7 +10100,9 @@
       <c r="C445" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D445" s="2"/>
+      <c r="D445" s="2">
+        <v>2599</v>
+      </c>
       <c r="E445" s="3">
         <v>4477.5</v>
       </c>
@@ -10119,7 +10121,9 @@
       <c r="C446" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D446" s="2"/>
+      <c r="D446" s="2">
+        <v>2923.5</v>
+      </c>
       <c r="E446" s="3">
         <v>3980</v>
       </c>
@@ -10138,7 +10142,9 @@
       <c r="C447" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D447" s="2"/>
+      <c r="D447" s="2">
+        <v>797</v>
+      </c>
       <c r="E447" s="3">
         <v>1492.5</v>
       </c>
@@ -10157,7 +10163,9 @@
       <c r="C448" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D448" s="2"/>
+      <c r="D448" s="2">
+        <v>2543.5</v>
+      </c>
       <c r="E448" s="3">
         <v>4170</v>
       </c>
@@ -10176,7 +10184,9 @@
       <c r="C449" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D449" s="2"/>
+      <c r="D449" s="2">
+        <v>1840.5</v>
+      </c>
       <c r="E449" s="3">
         <v>2780</v>
       </c>
@@ -10195,7 +10205,9 @@
       <c r="C450" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D450" s="2"/>
+      <c r="D450" s="2">
+        <v>1531.5</v>
+      </c>
       <c r="E450" s="3">
         <v>1710</v>
       </c>
@@ -10214,7 +10226,9 @@
       <c r="C451" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D451" s="2"/>
+      <c r="D451" s="2">
+        <v>2213.5</v>
+      </c>
       <c r="E451" s="3">
         <v>1610</v>
       </c>
@@ -10233,7 +10247,9 @@
       <c r="C452" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D452" s="2"/>
+      <c r="D452" s="2">
+        <v>528</v>
+      </c>
       <c r="E452" s="3">
         <v>1120</v>
       </c>
@@ -10252,7 +10268,9 @@
       <c r="C453" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D453" s="2"/>
+      <c r="D453" s="2">
+        <v>1146.5</v>
+      </c>
       <c r="E453" s="3">
         <v>1405</v>
       </c>
@@ -10271,7 +10289,9 @@
       <c r="C454" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="D454" s="2"/>
+      <c r="D454" s="2">
+        <v>709.5</v>
+      </c>
       <c r="E454" s="3">
         <v>1000</v>
       </c>
@@ -13252,7 +13272,7 @@
         <v>0</v>
       </c>
       <c r="AA14" s="8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AB14" s="8">
         <v>0</v>
@@ -13333,7 +13353,7 @@
         <v>1</v>
       </c>
       <c r="AA15" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB15" s="8">
         <v>0</v>
@@ -13414,7 +13434,7 @@
         <v>1</v>
       </c>
       <c r="AA16" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB16" s="8">
         <v>0</v>
@@ -13495,7 +13515,7 @@
         <v>3</v>
       </c>
       <c r="AA17" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB17" s="8">
         <v>0</v>
@@ -13576,7 +13596,7 @@
         <v>1</v>
       </c>
       <c r="AA18" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB18" s="8">
         <v>0</v>
@@ -13738,7 +13758,7 @@
         <v>1</v>
       </c>
       <c r="AA20" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB20" s="8">
         <v>0</v>
@@ -13900,7 +13920,7 @@
         <v>2</v>
       </c>
       <c r="AA22" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB22" s="8">
         <v>0</v>
@@ -13981,7 +14001,7 @@
         <v>0</v>
       </c>
       <c r="AA23" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB23" s="8">
         <v>0</v>

--- a/dados.xlsx
+++ b/dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://concresupersc-my.sharepoint.com/personal/marketing_concresupersc_onmicrosoft_com/Documents/Área de Trabalho/C.I.V/Dashbord/DASHBOARD-METAS-PROPOSTAS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="568" documentId="8_{A291900F-2FC4-4CBC-95EF-8FF0E06A2678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DC43AA1F-2E48-4B5D-9589-500C29BACCCA}"/>
+  <xr:revisionPtr revIDLastSave="619" documentId="8_{A291900F-2FC4-4CBC-95EF-8FF0E06A2678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3D3DAB29-07B1-4FF3-8CC3-C814EFC254B2}"/>
   <bookViews>
-    <workbookView xWindow="34785" yWindow="-3135" windowWidth="14610" windowHeight="15585" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dados Diários" sheetId="1" r:id="rId1"/>
@@ -18,9 +18,9 @@
     <sheet name="Propostas" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Dados Diários'!$A$1:$F$504</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Dados Diários'!$A$1:$F$764</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Metas 100%'!$A$1:$D$61</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Propostas!$A$1:$A$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Propostas!$A$1:$A$34</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1776" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2578" uniqueCount="72">
   <si>
     <t>Cidade</t>
   </si>
@@ -253,6 +253,9 @@
   </si>
   <si>
     <t xml:space="preserve">Lucas </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Setembro </t>
   </si>
 </sst>
 </file>
@@ -722,10 +725,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr>
+  <sheetPr filterMode="1">
     <tabColor rgb="FF1F4E79"/>
   </sheetPr>
-  <dimension ref="A1:J504"/>
+  <dimension ref="A1:J764"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.42578125" style="6" bestFit="1" customWidth="1"/>
@@ -760,7 +763,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>6</v>
       </c>
@@ -781,7 +784,7 @@
       </c>
       <c r="H2" s="7"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>6</v>
       </c>
@@ -802,7 +805,7 @@
       </c>
       <c r="H3" s="7"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>6</v>
       </c>
@@ -823,7 +826,7 @@
       </c>
       <c r="H4" s="7"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>11</v>
       </c>
@@ -844,7 +847,7 @@
       </c>
       <c r="H5" s="7"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>11</v>
       </c>
@@ -865,7 +868,7 @@
       </c>
       <c r="H6" s="7"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>24</v>
       </c>
@@ -886,7 +889,7 @@
       </c>
       <c r="H7" s="7"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>26</v>
       </c>
@@ -907,7 +910,7 @@
       </c>
       <c r="H8" s="7"/>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>28</v>
       </c>
@@ -928,7 +931,7 @@
       </c>
       <c r="H9" s="7"/>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
         <v>30</v>
       </c>
@@ -949,7 +952,7 @@
       </c>
       <c r="H10" s="7"/>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>6</v>
       </c>
@@ -970,7 +973,7 @@
       </c>
       <c r="H11" s="7"/>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>6</v>
       </c>
@@ -991,7 +994,7 @@
       </c>
       <c r="H12" s="7"/>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>6</v>
       </c>
@@ -1012,7 +1015,7 @@
       </c>
       <c r="H13" s="7"/>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
         <v>11</v>
       </c>
@@ -1033,7 +1036,7 @@
       </c>
       <c r="H14" s="7"/>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
         <v>11</v>
       </c>
@@ -1054,7 +1057,7 @@
       </c>
       <c r="H15" s="7"/>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
         <v>24</v>
       </c>
@@ -1075,7 +1078,7 @@
       </c>
       <c r="H16" s="7"/>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>26</v>
       </c>
@@ -1096,7 +1099,7 @@
       </c>
       <c r="H17" s="7"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
         <v>28</v>
       </c>
@@ -1117,7 +1120,7 @@
       </c>
       <c r="H18" s="7"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>30</v>
       </c>
@@ -1138,7 +1141,7 @@
       </c>
       <c r="H19" s="7"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>6</v>
       </c>
@@ -1159,7 +1162,7 @@
       </c>
       <c r="H20" s="7"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
         <v>6</v>
       </c>
@@ -1180,7 +1183,7 @@
       </c>
       <c r="H21" s="7"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
         <v>6</v>
       </c>
@@ -1201,7 +1204,7 @@
       </c>
       <c r="H22" s="7"/>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>11</v>
       </c>
@@ -1222,7 +1225,7 @@
       </c>
       <c r="H23" s="7"/>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>11</v>
       </c>
@@ -1243,7 +1246,7 @@
       </c>
       <c r="H24" s="7"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>24</v>
       </c>
@@ -1264,7 +1267,7 @@
       </c>
       <c r="H25" s="7"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
         <v>26</v>
       </c>
@@ -1285,7 +1288,7 @@
       </c>
       <c r="H26" s="7"/>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
         <v>28</v>
       </c>
@@ -1306,7 +1309,7 @@
       </c>
       <c r="H27" s="7"/>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
         <v>30</v>
       </c>
@@ -1327,7 +1330,7 @@
       </c>
       <c r="H28" s="7"/>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>6</v>
       </c>
@@ -1348,7 +1351,7 @@
       </c>
       <c r="H29" s="7"/>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
         <v>6</v>
       </c>
@@ -1369,7 +1372,7 @@
       </c>
       <c r="H30" s="7"/>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
         <v>6</v>
       </c>
@@ -1390,7 +1393,7 @@
       </c>
       <c r="H31" s="7"/>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
         <v>11</v>
       </c>
@@ -1411,7 +1414,7 @@
       </c>
       <c r="H32" s="7"/>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
         <v>11</v>
       </c>
@@ -1432,7 +1435,7 @@
       </c>
       <c r="H33" s="7"/>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
         <v>24</v>
       </c>
@@ -1453,7 +1456,7 @@
       </c>
       <c r="H34" s="7"/>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
         <v>26</v>
       </c>
@@ -1474,7 +1477,7 @@
       </c>
       <c r="H35" s="7"/>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
         <v>28</v>
       </c>
@@ -1495,7 +1498,7 @@
       </c>
       <c r="H36" s="7"/>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
         <v>30</v>
       </c>
@@ -1516,7 +1519,7 @@
       </c>
       <c r="H37" s="7"/>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
         <v>6</v>
       </c>
@@ -1537,7 +1540,7 @@
       </c>
       <c r="H38" s="7"/>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
         <v>6</v>
       </c>
@@ -1558,7 +1561,7 @@
       </c>
       <c r="H39" s="7"/>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
         <v>6</v>
       </c>
@@ -1579,7 +1582,7 @@
       </c>
       <c r="H40" s="7"/>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
         <v>11</v>
       </c>
@@ -1600,7 +1603,7 @@
       </c>
       <c r="H41" s="7"/>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
         <v>11</v>
       </c>
@@ -1621,7 +1624,7 @@
       </c>
       <c r="H42" s="7"/>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
         <v>24</v>
       </c>
@@ -1642,7 +1645,7 @@
       </c>
       <c r="H43" s="7"/>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
         <v>26</v>
       </c>
@@ -1663,7 +1666,7 @@
       </c>
       <c r="H44" s="7"/>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
         <v>28</v>
       </c>
@@ -1684,7 +1687,7 @@
       </c>
       <c r="H45" s="7"/>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
         <v>30</v>
       </c>
@@ -1705,7 +1708,7 @@
       </c>
       <c r="H46" s="7"/>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
         <v>6</v>
       </c>
@@ -1726,7 +1729,7 @@
       </c>
       <c r="H47" s="7"/>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
         <v>6</v>
       </c>
@@ -1747,7 +1750,7 @@
       </c>
       <c r="H48" s="7"/>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
         <v>6</v>
       </c>
@@ -1768,7 +1771,7 @@
       </c>
       <c r="H49" s="7"/>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
         <v>11</v>
       </c>
@@ -1789,7 +1792,7 @@
       </c>
       <c r="H50" s="7"/>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
         <v>11</v>
       </c>
@@ -1810,7 +1813,7 @@
       </c>
       <c r="H51" s="7"/>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
         <v>24</v>
       </c>
@@ -1831,7 +1834,7 @@
       </c>
       <c r="H52" s="7"/>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
         <v>26</v>
       </c>
@@ -1852,7 +1855,7 @@
       </c>
       <c r="H53" s="7"/>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
         <v>28</v>
       </c>
@@ -1873,7 +1876,7 @@
       </c>
       <c r="H54" s="7"/>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
         <v>30</v>
       </c>
@@ -1894,7 +1897,7 @@
       </c>
       <c r="H55" s="7"/>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
         <v>6</v>
       </c>
@@ -1915,7 +1918,7 @@
       </c>
       <c r="H56" s="7"/>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
         <v>6</v>
       </c>
@@ -1936,7 +1939,7 @@
       </c>
       <c r="H57" s="7"/>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
         <v>6</v>
       </c>
@@ -1957,7 +1960,7 @@
       </c>
       <c r="H58" s="7"/>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
         <v>11</v>
       </c>
@@ -1978,7 +1981,7 @@
       </c>
       <c r="H59" s="7"/>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
         <v>11</v>
       </c>
@@ -1999,7 +2002,7 @@
       </c>
       <c r="H60" s="7"/>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
         <v>24</v>
       </c>
@@ -2020,7 +2023,7 @@
       </c>
       <c r="H61" s="7"/>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
         <v>26</v>
       </c>
@@ -2041,7 +2044,7 @@
       </c>
       <c r="H62" s="7"/>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
         <v>28</v>
       </c>
@@ -2062,7 +2065,7 @@
       </c>
       <c r="H63" s="7"/>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
         <v>30</v>
       </c>
@@ -2083,7 +2086,7 @@
       </c>
       <c r="H64" s="7"/>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
         <v>6</v>
       </c>
@@ -2104,7 +2107,7 @@
       </c>
       <c r="H65" s="7"/>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
         <v>6</v>
       </c>
@@ -2125,7 +2128,7 @@
       </c>
       <c r="H66" s="7"/>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
         <v>6</v>
       </c>
@@ -2146,7 +2149,7 @@
       </c>
       <c r="H67" s="7"/>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
         <v>11</v>
       </c>
@@ -2167,7 +2170,7 @@
       </c>
       <c r="H68" s="7"/>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
         <v>11</v>
       </c>
@@ -2188,7 +2191,7 @@
       </c>
       <c r="H69" s="7"/>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
         <v>24</v>
       </c>
@@ -2209,7 +2212,7 @@
       </c>
       <c r="H70" s="7"/>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" s="4" t="s">
         <v>26</v>
       </c>
@@ -2230,7 +2233,7 @@
       </c>
       <c r="H71" s="7"/>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
         <v>28</v>
       </c>
@@ -2251,7 +2254,7 @@
       </c>
       <c r="H72" s="7"/>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" s="4" t="s">
         <v>30</v>
       </c>
@@ -2272,7 +2275,7 @@
       </c>
       <c r="H73" s="7"/>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
         <v>6</v>
       </c>
@@ -2293,7 +2296,7 @@
       </c>
       <c r="H74" s="7"/>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" s="4" t="s">
         <v>6</v>
       </c>
@@ -2314,7 +2317,7 @@
       </c>
       <c r="H75" s="7"/>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
         <v>6</v>
       </c>
@@ -2335,7 +2338,7 @@
       </c>
       <c r="H76" s="7"/>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" s="4" t="s">
         <v>11</v>
       </c>
@@ -2356,7 +2359,7 @@
       </c>
       <c r="H77" s="7"/>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
         <v>11</v>
       </c>
@@ -2377,7 +2380,7 @@
       </c>
       <c r="H78" s="7"/>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" s="4" t="s">
         <v>24</v>
       </c>
@@ -2398,7 +2401,7 @@
       </c>
       <c r="H79" s="7"/>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
         <v>26</v>
       </c>
@@ -2419,7 +2422,7 @@
       </c>
       <c r="H80" s="7"/>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" s="4" t="s">
         <v>28</v>
       </c>
@@ -2440,7 +2443,7 @@
       </c>
       <c r="H81" s="7"/>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
         <v>30</v>
       </c>
@@ -2461,7 +2464,7 @@
       </c>
       <c r="H82" s="7"/>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" s="4" t="s">
         <v>6</v>
       </c>
@@ -2482,7 +2485,7 @@
       </c>
       <c r="H83" s="7"/>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
         <v>6</v>
       </c>
@@ -2503,7 +2506,7 @@
       </c>
       <c r="H84" s="7"/>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" s="4" t="s">
         <v>6</v>
       </c>
@@ -2524,7 +2527,7 @@
       </c>
       <c r="H85" s="7"/>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
         <v>11</v>
       </c>
@@ -2545,7 +2548,7 @@
       </c>
       <c r="H86" s="7"/>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" s="4" t="s">
         <v>11</v>
       </c>
@@ -2566,7 +2569,7 @@
       </c>
       <c r="H87" s="7"/>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
         <v>24</v>
       </c>
@@ -2587,7 +2590,7 @@
       </c>
       <c r="H88" s="7"/>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" s="4" t="s">
         <v>26</v>
       </c>
@@ -2608,7 +2611,7 @@
       </c>
       <c r="H89" s="7"/>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
         <v>28</v>
       </c>
@@ -2629,7 +2632,7 @@
       </c>
       <c r="H90" s="7"/>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" s="4" t="s">
         <v>30</v>
       </c>
@@ -2650,7 +2653,7 @@
       </c>
       <c r="H91" s="7"/>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
         <v>6</v>
       </c>
@@ -2671,7 +2674,7 @@
       </c>
       <c r="H92" s="7"/>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" s="4" t="s">
         <v>6</v>
       </c>
@@ -2692,7 +2695,7 @@
       </c>
       <c r="H93" s="7"/>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
         <v>6</v>
       </c>
@@ -2713,7 +2716,7 @@
       </c>
       <c r="H94" s="7"/>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" s="4" t="s">
         <v>11</v>
       </c>
@@ -2734,7 +2737,7 @@
       </c>
       <c r="H95" s="7"/>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
         <v>11</v>
       </c>
@@ -2755,7 +2758,7 @@
       </c>
       <c r="H96" s="7"/>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" s="4" t="s">
         <v>24</v>
       </c>
@@ -2776,7 +2779,7 @@
       </c>
       <c r="H97" s="7"/>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
         <v>26</v>
       </c>
@@ -2797,7 +2800,7 @@
       </c>
       <c r="H98" s="7"/>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" s="4" t="s">
         <v>28</v>
       </c>
@@ -2818,7 +2821,7 @@
       </c>
       <c r="H99" s="7"/>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
         <v>30</v>
       </c>
@@ -2839,7 +2842,7 @@
       </c>
       <c r="H100" s="7"/>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" s="4" t="s">
         <v>6</v>
       </c>
@@ -2860,7 +2863,7 @@
       </c>
       <c r="H101" s="7"/>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
         <v>6</v>
       </c>
@@ -2881,7 +2884,7 @@
       </c>
       <c r="H102" s="7"/>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" s="4" t="s">
         <v>6</v>
       </c>
@@ -2902,7 +2905,7 @@
       </c>
       <c r="H103" s="7"/>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
         <v>11</v>
       </c>
@@ -2923,7 +2926,7 @@
       </c>
       <c r="H104" s="7"/>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" s="4" t="s">
         <v>11</v>
       </c>
@@ -2944,7 +2947,7 @@
       </c>
       <c r="H105" s="7"/>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
         <v>24</v>
       </c>
@@ -2965,7 +2968,7 @@
       </c>
       <c r="H106" s="7"/>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" s="4" t="s">
         <v>26</v>
       </c>
@@ -2986,7 +2989,7 @@
       </c>
       <c r="H107" s="7"/>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
         <v>28</v>
       </c>
@@ -3007,7 +3010,7 @@
       </c>
       <c r="H108" s="7"/>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" s="4" t="s">
         <v>30</v>
       </c>
@@ -3028,7 +3031,7 @@
       </c>
       <c r="H109" s="7"/>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
         <v>6</v>
       </c>
@@ -3049,7 +3052,7 @@
       </c>
       <c r="H110" s="7"/>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" s="4" t="s">
         <v>6</v>
       </c>
@@ -3070,7 +3073,7 @@
       </c>
       <c r="H111" s="7"/>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
         <v>6</v>
       </c>
@@ -3091,7 +3094,7 @@
       </c>
       <c r="H112" s="7"/>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" s="4" t="s">
         <v>11</v>
       </c>
@@ -3112,7 +3115,7 @@
       </c>
       <c r="H113" s="7"/>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
         <v>11</v>
       </c>
@@ -3133,7 +3136,7 @@
       </c>
       <c r="H114" s="7"/>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" s="4" t="s">
         <v>24</v>
       </c>
@@ -3154,7 +3157,7 @@
       </c>
       <c r="H115" s="7"/>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
         <v>26</v>
       </c>
@@ -3175,7 +3178,7 @@
       </c>
       <c r="H116" s="7"/>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" s="4" t="s">
         <v>28</v>
       </c>
@@ -3196,7 +3199,7 @@
       </c>
       <c r="H117" s="7"/>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
         <v>30</v>
       </c>
@@ -3217,7 +3220,7 @@
       </c>
       <c r="H118" s="7"/>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" s="4" t="s">
         <v>6</v>
       </c>
@@ -3238,7 +3241,7 @@
       </c>
       <c r="H119" s="7"/>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
         <v>6</v>
       </c>
@@ -3259,7 +3262,7 @@
       </c>
       <c r="H120" s="7"/>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" s="4" t="s">
         <v>6</v>
       </c>
@@ -3280,7 +3283,7 @@
       </c>
       <c r="H121" s="7"/>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
         <v>11</v>
       </c>
@@ -3301,7 +3304,7 @@
       </c>
       <c r="H122" s="7"/>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" s="4" t="s">
         <v>11</v>
       </c>
@@ -3322,7 +3325,7 @@
       </c>
       <c r="H123" s="7"/>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
         <v>24</v>
       </c>
@@ -3343,7 +3346,7 @@
       </c>
       <c r="H124" s="7"/>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" s="4" t="s">
         <v>26</v>
       </c>
@@ -3364,7 +3367,7 @@
       </c>
       <c r="H125" s="7"/>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
         <v>28</v>
       </c>
@@ -3385,7 +3388,7 @@
       </c>
       <c r="H126" s="7"/>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" s="4" t="s">
         <v>30</v>
       </c>
@@ -3406,7 +3409,7 @@
       </c>
       <c r="H127" s="7"/>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
         <v>6</v>
       </c>
@@ -3427,7 +3430,7 @@
       </c>
       <c r="H128" s="7"/>
     </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" s="4" t="s">
         <v>6</v>
       </c>
@@ -3448,7 +3451,7 @@
       </c>
       <c r="H129" s="7"/>
     </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
         <v>6</v>
       </c>
@@ -3469,7 +3472,7 @@
       </c>
       <c r="H130" s="7"/>
     </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" s="4" t="s">
         <v>11</v>
       </c>
@@ -3490,7 +3493,7 @@
       </c>
       <c r="H131" s="7"/>
     </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
         <v>11</v>
       </c>
@@ -3511,7 +3514,7 @@
       </c>
       <c r="H132" s="7"/>
     </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" s="4" t="s">
         <v>24</v>
       </c>
@@ -3532,7 +3535,7 @@
       </c>
       <c r="H133" s="7"/>
     </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
         <v>26</v>
       </c>
@@ -3553,7 +3556,7 @@
       </c>
       <c r="H134" s="7"/>
     </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" s="4" t="s">
         <v>28</v>
       </c>
@@ -3574,7 +3577,7 @@
       </c>
       <c r="H135" s="7"/>
     </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
         <v>30</v>
       </c>
@@ -3595,7 +3598,7 @@
       </c>
       <c r="H136" s="7"/>
     </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" s="4" t="s">
         <v>6</v>
       </c>
@@ -3616,7 +3619,7 @@
       </c>
       <c r="H137" s="7"/>
     </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
         <v>6</v>
       </c>
@@ -3637,7 +3640,7 @@
       </c>
       <c r="H138" s="7"/>
     </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" s="4" t="s">
         <v>6</v>
       </c>
@@ -3658,7 +3661,7 @@
       </c>
       <c r="H139" s="7"/>
     </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
         <v>11</v>
       </c>
@@ -3679,7 +3682,7 @@
       </c>
       <c r="H140" s="7"/>
     </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" s="4" t="s">
         <v>11</v>
       </c>
@@ -3700,7 +3703,7 @@
       </c>
       <c r="H141" s="7"/>
     </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
         <v>24</v>
       </c>
@@ -3721,7 +3724,7 @@
       </c>
       <c r="H142" s="7"/>
     </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" s="4" t="s">
         <v>26</v>
       </c>
@@ -3742,7 +3745,7 @@
       </c>
       <c r="H143" s="7"/>
     </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
         <v>28</v>
       </c>
@@ -3763,7 +3766,7 @@
       </c>
       <c r="H144" s="7"/>
     </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145" s="4" t="s">
         <v>30</v>
       </c>
@@ -3784,7 +3787,7 @@
       </c>
       <c r="H145" s="7"/>
     </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
         <v>6</v>
       </c>
@@ -3805,7 +3808,7 @@
       </c>
       <c r="H146" s="7"/>
     </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" s="4" t="s">
         <v>6</v>
       </c>
@@ -3826,7 +3829,7 @@
       </c>
       <c r="H147" s="7"/>
     </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
         <v>6</v>
       </c>
@@ -3847,7 +3850,7 @@
       </c>
       <c r="H148" s="7"/>
     </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149" s="4" t="s">
         <v>11</v>
       </c>
@@ -3868,7 +3871,7 @@
       </c>
       <c r="H149" s="7"/>
     </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
         <v>11</v>
       </c>
@@ -3889,7 +3892,7 @@
       </c>
       <c r="H150" s="7"/>
     </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151" s="4" t="s">
         <v>24</v>
       </c>
@@ -3910,7 +3913,7 @@
       </c>
       <c r="H151" s="7"/>
     </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
         <v>26</v>
       </c>
@@ -3931,7 +3934,7 @@
       </c>
       <c r="H152" s="7"/>
     </row>
-    <row r="153" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153" s="4" t="s">
         <v>28</v>
       </c>
@@ -3952,7 +3955,7 @@
       </c>
       <c r="H153" s="7"/>
     </row>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
         <v>30</v>
       </c>
@@ -3973,7 +3976,7 @@
       </c>
       <c r="H154" s="7"/>
     </row>
-    <row r="155" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155" s="4" t="s">
         <v>6</v>
       </c>
@@ -3994,7 +3997,7 @@
       </c>
       <c r="H155" s="7"/>
     </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156" s="4" t="s">
         <v>6</v>
       </c>
@@ -4015,7 +4018,7 @@
       </c>
       <c r="H156" s="7"/>
     </row>
-    <row r="157" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157" s="4" t="s">
         <v>6</v>
       </c>
@@ -4036,7 +4039,7 @@
       </c>
       <c r="H157" s="7"/>
     </row>
-    <row r="158" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158" s="4" t="s">
         <v>11</v>
       </c>
@@ -4057,7 +4060,7 @@
       </c>
       <c r="H158" s="7"/>
     </row>
-    <row r="159" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159" s="4" t="s">
         <v>11</v>
       </c>
@@ -4078,7 +4081,7 @@
       </c>
       <c r="H159" s="7"/>
     </row>
-    <row r="160" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160" s="4" t="s">
         <v>24</v>
       </c>
@@ -4099,7 +4102,7 @@
       </c>
       <c r="H160" s="7"/>
     </row>
-    <row r="161" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161" s="4" t="s">
         <v>26</v>
       </c>
@@ -4120,7 +4123,7 @@
       </c>
       <c r="H161" s="7"/>
     </row>
-    <row r="162" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162" s="4" t="s">
         <v>28</v>
       </c>
@@ -4141,7 +4144,7 @@
       </c>
       <c r="H162" s="7"/>
     </row>
-    <row r="163" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163" s="4" t="s">
         <v>30</v>
       </c>
@@ -4162,7 +4165,7 @@
       </c>
       <c r="H163" s="7"/>
     </row>
-    <row r="164" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164" s="4" t="s">
         <v>6</v>
       </c>
@@ -4183,7 +4186,7 @@
       </c>
       <c r="H164" s="7"/>
     </row>
-    <row r="165" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165" s="4" t="s">
         <v>6</v>
       </c>
@@ -4204,7 +4207,7 @@
       </c>
       <c r="H165" s="7"/>
     </row>
-    <row r="166" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166" s="4" t="s">
         <v>6</v>
       </c>
@@ -4225,7 +4228,7 @@
       </c>
       <c r="H166" s="7"/>
     </row>
-    <row r="167" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167" s="4" t="s">
         <v>11</v>
       </c>
@@ -4246,7 +4249,7 @@
       </c>
       <c r="H167" s="7"/>
     </row>
-    <row r="168" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168" s="4" t="s">
         <v>11</v>
       </c>
@@ -4267,7 +4270,7 @@
       </c>
       <c r="H168" s="7"/>
     </row>
-    <row r="169" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A169" s="4" t="s">
         <v>24</v>
       </c>
@@ -4288,7 +4291,7 @@
       </c>
       <c r="H169" s="7"/>
     </row>
-    <row r="170" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A170" s="4" t="s">
         <v>26</v>
       </c>
@@ -4309,7 +4312,7 @@
       </c>
       <c r="H170" s="7"/>
     </row>
-    <row r="171" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A171" s="4" t="s">
         <v>28</v>
       </c>
@@ -4330,7 +4333,7 @@
       </c>
       <c r="H171" s="7"/>
     </row>
-    <row r="172" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A172" s="4" t="s">
         <v>30</v>
       </c>
@@ -4351,7 +4354,7 @@
       </c>
       <c r="H172" s="7"/>
     </row>
-    <row r="173" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173" s="4" t="s">
         <v>6</v>
       </c>
@@ -4372,7 +4375,7 @@
       </c>
       <c r="H173" s="7"/>
     </row>
-    <row r="174" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A174" s="4" t="s">
         <v>6</v>
       </c>
@@ -4393,7 +4396,7 @@
       </c>
       <c r="H174" s="7"/>
     </row>
-    <row r="175" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175" s="4" t="s">
         <v>6</v>
       </c>
@@ -4414,7 +4417,7 @@
       </c>
       <c r="H175" s="7"/>
     </row>
-    <row r="176" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176" s="4" t="s">
         <v>11</v>
       </c>
@@ -4435,7 +4438,7 @@
       </c>
       <c r="H176" s="7"/>
     </row>
-    <row r="177" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177" s="4" t="s">
         <v>11</v>
       </c>
@@ -4456,7 +4459,7 @@
       </c>
       <c r="H177" s="7"/>
     </row>
-    <row r="178" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A178" s="4" t="s">
         <v>24</v>
       </c>
@@ -4477,7 +4480,7 @@
       </c>
       <c r="H178" s="7"/>
     </row>
-    <row r="179" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A179" s="4" t="s">
         <v>26</v>
       </c>
@@ -4498,7 +4501,7 @@
       </c>
       <c r="H179" s="7"/>
     </row>
-    <row r="180" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A180" s="4" t="s">
         <v>28</v>
       </c>
@@ -4519,7 +4522,7 @@
       </c>
       <c r="H180" s="7"/>
     </row>
-    <row r="181" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A181" s="4" t="s">
         <v>30</v>
       </c>
@@ -4540,7 +4543,7 @@
       </c>
       <c r="H181" s="7"/>
     </row>
-    <row r="182" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A182" s="4" t="s">
         <v>6</v>
       </c>
@@ -4561,7 +4564,7 @@
       </c>
       <c r="H182" s="7"/>
     </row>
-    <row r="183" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A183" s="4" t="s">
         <v>6</v>
       </c>
@@ -4582,7 +4585,7 @@
       </c>
       <c r="H183" s="7"/>
     </row>
-    <row r="184" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A184" s="4" t="s">
         <v>6</v>
       </c>
@@ -4603,7 +4606,7 @@
       </c>
       <c r="H184" s="7"/>
     </row>
-    <row r="185" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A185" s="4" t="s">
         <v>11</v>
       </c>
@@ -4624,7 +4627,7 @@
       </c>
       <c r="H185" s="7"/>
     </row>
-    <row r="186" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A186" s="4" t="s">
         <v>11</v>
       </c>
@@ -4645,7 +4648,7 @@
       </c>
       <c r="H186" s="7"/>
     </row>
-    <row r="187" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A187" s="4" t="s">
         <v>24</v>
       </c>
@@ -4666,7 +4669,7 @@
       </c>
       <c r="H187" s="7"/>
     </row>
-    <row r="188" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A188" s="4" t="s">
         <v>26</v>
       </c>
@@ -4687,7 +4690,7 @@
       </c>
       <c r="H188" s="7"/>
     </row>
-    <row r="189" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A189" s="4" t="s">
         <v>28</v>
       </c>
@@ -4708,7 +4711,7 @@
       </c>
       <c r="H189" s="7"/>
     </row>
-    <row r="190" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A190" s="4" t="s">
         <v>30</v>
       </c>
@@ -4729,7 +4732,7 @@
       </c>
       <c r="H190" s="7"/>
     </row>
-    <row r="191" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A191" s="4" t="s">
         <v>6</v>
       </c>
@@ -4750,7 +4753,7 @@
       </c>
       <c r="H191" s="7"/>
     </row>
-    <row r="192" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A192" s="4" t="s">
         <v>6</v>
       </c>
@@ -4771,7 +4774,7 @@
       </c>
       <c r="H192" s="7"/>
     </row>
-    <row r="193" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A193" s="4" t="s">
         <v>6</v>
       </c>
@@ -4792,7 +4795,7 @@
       </c>
       <c r="H193" s="7"/>
     </row>
-    <row r="194" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A194" s="4" t="s">
         <v>11</v>
       </c>
@@ -4813,7 +4816,7 @@
       </c>
       <c r="H194" s="7"/>
     </row>
-    <row r="195" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A195" s="4" t="s">
         <v>11</v>
       </c>
@@ -4834,7 +4837,7 @@
       </c>
       <c r="H195" s="7"/>
     </row>
-    <row r="196" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A196" s="4" t="s">
         <v>24</v>
       </c>
@@ -4855,7 +4858,7 @@
       </c>
       <c r="H196" s="7"/>
     </row>
-    <row r="197" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A197" s="4" t="s">
         <v>26</v>
       </c>
@@ -4876,7 +4879,7 @@
       </c>
       <c r="H197" s="7"/>
     </row>
-    <row r="198" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A198" s="4" t="s">
         <v>28</v>
       </c>
@@ -4897,7 +4900,7 @@
       </c>
       <c r="H198" s="7"/>
     </row>
-    <row r="199" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A199" s="4" t="s">
         <v>30</v>
       </c>
@@ -4918,7 +4921,7 @@
       </c>
       <c r="H199" s="7"/>
     </row>
-    <row r="200" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A200" s="4" t="s">
         <v>6</v>
       </c>
@@ -4939,7 +4942,7 @@
       </c>
       <c r="H200" s="7"/>
     </row>
-    <row r="201" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A201" s="4" t="s">
         <v>6</v>
       </c>
@@ -4960,7 +4963,7 @@
       </c>
       <c r="H201" s="7"/>
     </row>
-    <row r="202" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A202" s="4" t="s">
         <v>6</v>
       </c>
@@ -4981,7 +4984,7 @@
       </c>
       <c r="H202" s="7"/>
     </row>
-    <row r="203" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A203" s="4" t="s">
         <v>11</v>
       </c>
@@ -5002,7 +5005,7 @@
       </c>
       <c r="H203" s="7"/>
     </row>
-    <row r="204" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A204" s="4" t="s">
         <v>11</v>
       </c>
@@ -5023,7 +5026,7 @@
       </c>
       <c r="H204" s="7"/>
     </row>
-    <row r="205" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A205" s="4" t="s">
         <v>24</v>
       </c>
@@ -5044,7 +5047,7 @@
       </c>
       <c r="H205" s="7"/>
     </row>
-    <row r="206" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A206" s="4" t="s">
         <v>26</v>
       </c>
@@ -5065,7 +5068,7 @@
       </c>
       <c r="H206" s="7"/>
     </row>
-    <row r="207" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A207" s="4" t="s">
         <v>28</v>
       </c>
@@ -5086,7 +5089,7 @@
       </c>
       <c r="H207" s="7"/>
     </row>
-    <row r="208" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A208" s="4" t="s">
         <v>30</v>
       </c>
@@ -5107,7 +5110,7 @@
       </c>
       <c r="H208" s="7"/>
     </row>
-    <row r="209" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A209" s="4" t="s">
         <v>6</v>
       </c>
@@ -5128,7 +5131,7 @@
       </c>
       <c r="H209" s="7"/>
     </row>
-    <row r="210" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A210" s="4" t="s">
         <v>6</v>
       </c>
@@ -5149,7 +5152,7 @@
       </c>
       <c r="H210" s="7"/>
     </row>
-    <row r="211" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A211" s="4" t="s">
         <v>6</v>
       </c>
@@ -5170,7 +5173,7 @@
       </c>
       <c r="H211" s="7"/>
     </row>
-    <row r="212" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A212" s="4" t="s">
         <v>11</v>
       </c>
@@ -5191,7 +5194,7 @@
       </c>
       <c r="H212" s="7"/>
     </row>
-    <row r="213" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A213" s="4" t="s">
         <v>11</v>
       </c>
@@ -5212,7 +5215,7 @@
       </c>
       <c r="H213" s="7"/>
     </row>
-    <row r="214" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A214" s="4" t="s">
         <v>24</v>
       </c>
@@ -5233,7 +5236,7 @@
       </c>
       <c r="H214" s="7"/>
     </row>
-    <row r="215" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A215" s="4" t="s">
         <v>26</v>
       </c>
@@ -5254,7 +5257,7 @@
       </c>
       <c r="H215" s="7"/>
     </row>
-    <row r="216" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A216" s="4" t="s">
         <v>28</v>
       </c>
@@ -5275,7 +5278,7 @@
       </c>
       <c r="H216" s="7"/>
     </row>
-    <row r="217" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A217" s="4" t="s">
         <v>30</v>
       </c>
@@ -5296,7 +5299,7 @@
       </c>
       <c r="H217" s="7"/>
     </row>
-    <row r="218" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A218" s="4" t="s">
         <v>6</v>
       </c>
@@ -5317,7 +5320,7 @@
       </c>
       <c r="H218" s="7"/>
     </row>
-    <row r="219" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A219" s="4" t="s">
         <v>6</v>
       </c>
@@ -5338,7 +5341,7 @@
       </c>
       <c r="H219" s="7"/>
     </row>
-    <row r="220" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A220" s="4" t="s">
         <v>6</v>
       </c>
@@ -5359,7 +5362,7 @@
       </c>
       <c r="H220" s="7"/>
     </row>
-    <row r="221" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A221" s="4" t="s">
         <v>11</v>
       </c>
@@ -5380,7 +5383,7 @@
       </c>
       <c r="H221" s="7"/>
     </row>
-    <row r="222" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A222" s="4" t="s">
         <v>11</v>
       </c>
@@ -5401,7 +5404,7 @@
       </c>
       <c r="H222" s="7"/>
     </row>
-    <row r="223" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A223" s="4" t="s">
         <v>24</v>
       </c>
@@ -5422,7 +5425,7 @@
       </c>
       <c r="H223" s="7"/>
     </row>
-    <row r="224" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A224" s="4" t="s">
         <v>26</v>
       </c>
@@ -5443,7 +5446,7 @@
       </c>
       <c r="H224" s="7"/>
     </row>
-    <row r="225" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A225" s="4" t="s">
         <v>28</v>
       </c>
@@ -5464,7 +5467,7 @@
       </c>
       <c r="H225" s="7"/>
     </row>
-    <row r="226" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A226" s="4" t="s">
         <v>30</v>
       </c>
@@ -5485,7 +5488,7 @@
       </c>
       <c r="H226" s="7"/>
     </row>
-    <row r="227" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A227" s="4" t="s">
         <v>6</v>
       </c>
@@ -5506,7 +5509,7 @@
       </c>
       <c r="H227" s="7"/>
     </row>
-    <row r="228" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A228" s="4" t="s">
         <v>6</v>
       </c>
@@ -5527,7 +5530,7 @@
       </c>
       <c r="H228" s="7"/>
     </row>
-    <row r="229" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A229" s="4" t="s">
         <v>6</v>
       </c>
@@ -5548,7 +5551,7 @@
       </c>
       <c r="H229" s="7"/>
     </row>
-    <row r="230" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A230" s="4" t="s">
         <v>11</v>
       </c>
@@ -5569,7 +5572,7 @@
       </c>
       <c r="H230" s="7"/>
     </row>
-    <row r="231" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A231" s="4" t="s">
         <v>11</v>
       </c>
@@ -5590,7 +5593,7 @@
       </c>
       <c r="H231" s="7"/>
     </row>
-    <row r="232" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A232" s="4" t="s">
         <v>24</v>
       </c>
@@ -5611,7 +5614,7 @@
       </c>
       <c r="H232" s="7"/>
     </row>
-    <row r="233" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A233" s="4" t="s">
         <v>26</v>
       </c>
@@ -5632,7 +5635,7 @@
       </c>
       <c r="H233" s="7"/>
     </row>
-    <row r="234" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A234" s="4" t="s">
         <v>28</v>
       </c>
@@ -5653,7 +5656,7 @@
       </c>
       <c r="H234" s="7"/>
     </row>
-    <row r="235" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A235" s="4" t="s">
         <v>30</v>
       </c>
@@ -5674,7 +5677,7 @@
       </c>
       <c r="H235" s="7"/>
     </row>
-    <row r="236" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A236" s="4" t="s">
         <v>6</v>
       </c>
@@ -5696,7 +5699,7 @@
       <c r="H236" s="7"/>
       <c r="J236" s="7"/>
     </row>
-    <row r="237" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A237" s="4" t="s">
         <v>6</v>
       </c>
@@ -5718,7 +5721,7 @@
       <c r="H237" s="7"/>
       <c r="J237" s="7"/>
     </row>
-    <row r="238" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A238" s="4" t="s">
         <v>6</v>
       </c>
@@ -5740,7 +5743,7 @@
       <c r="H238" s="7"/>
       <c r="J238" s="7"/>
     </row>
-    <row r="239" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A239" s="4" t="s">
         <v>11</v>
       </c>
@@ -5762,7 +5765,7 @@
       <c r="H239" s="7"/>
       <c r="J239" s="7"/>
     </row>
-    <row r="240" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A240" s="4" t="s">
         <v>11</v>
       </c>
@@ -5784,7 +5787,7 @@
       <c r="H240" s="7"/>
       <c r="J240" s="7"/>
     </row>
-    <row r="241" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A241" s="4" t="s">
         <v>24</v>
       </c>
@@ -5806,7 +5809,7 @@
       <c r="H241" s="7"/>
       <c r="J241" s="7"/>
     </row>
-    <row r="242" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A242" s="4" t="s">
         <v>26</v>
       </c>
@@ -5828,7 +5831,7 @@
       <c r="H242" s="7"/>
       <c r="J242" s="7"/>
     </row>
-    <row r="243" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A243" s="4" t="s">
         <v>28</v>
       </c>
@@ -5850,7 +5853,7 @@
       <c r="H243" s="7"/>
       <c r="J243" s="7"/>
     </row>
-    <row r="244" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A244" s="4" t="s">
         <v>30</v>
       </c>
@@ -10310,7 +10313,9 @@
       <c r="C455" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D455" s="2"/>
+      <c r="D455" s="2">
+        <v>2752.5</v>
+      </c>
       <c r="E455" s="3">
         <v>4477.5</v>
       </c>
@@ -10329,7 +10334,9 @@
       <c r="C456" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D456" s="2"/>
+      <c r="D456" s="2">
+        <v>3009</v>
+      </c>
       <c r="E456" s="3">
         <v>3980</v>
       </c>
@@ -10348,7 +10355,9 @@
       <c r="C457" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D457" s="2"/>
+      <c r="D457" s="2">
+        <v>850.5</v>
+      </c>
       <c r="E457" s="3">
         <v>1492.5</v>
       </c>
@@ -10367,7 +10376,9 @@
       <c r="C458" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D458" s="2"/>
+      <c r="D458" s="2">
+        <v>2663</v>
+      </c>
       <c r="E458" s="3">
         <v>4170</v>
       </c>
@@ -10386,7 +10397,9 @@
       <c r="C459" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D459" s="2"/>
+      <c r="D459" s="2">
+        <v>2075.5</v>
+      </c>
       <c r="E459" s="3">
         <v>2780</v>
       </c>
@@ -10405,7 +10418,9 @@
       <c r="C460" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D460" s="2"/>
+      <c r="D460" s="2">
+        <v>1586.5</v>
+      </c>
       <c r="E460" s="3">
         <v>1710</v>
       </c>
@@ -10424,7 +10439,9 @@
       <c r="C461" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D461" s="2"/>
+      <c r="D461" s="2">
+        <v>2342</v>
+      </c>
       <c r="E461" s="3">
         <v>1610</v>
       </c>
@@ -10443,7 +10460,9 @@
       <c r="C462" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D462" s="2"/>
+      <c r="D462" s="2">
+        <v>592</v>
+      </c>
       <c r="E462" s="3">
         <v>1120</v>
       </c>
@@ -10462,7 +10481,9 @@
       <c r="C463" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D463" s="2"/>
+      <c r="D463" s="2">
+        <v>1170</v>
+      </c>
       <c r="E463" s="3">
         <v>1405</v>
       </c>
@@ -10481,7 +10502,9 @@
       <c r="C464" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="D464" s="2"/>
+      <c r="D464" s="2">
+        <v>743.5</v>
+      </c>
       <c r="E464" s="3">
         <v>1000</v>
       </c>
@@ -11240,8 +11263,4174 @@
         <v>46265</v>
       </c>
     </row>
+    <row r="505" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A505" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B505" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C505" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D505" s="2"/>
+      <c r="E505" s="3"/>
+      <c r="F505" s="5">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="506" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A506" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B506" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C506" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D506" s="2"/>
+      <c r="E506" s="3"/>
+      <c r="F506" s="5">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="507" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A507" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B507" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C507" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D507" s="2"/>
+      <c r="E507" s="3"/>
+      <c r="F507" s="5">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="508" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A508" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B508" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C508" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D508" s="2"/>
+      <c r="E508" s="3"/>
+      <c r="F508" s="5">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="509" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A509" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B509" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C509" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D509" s="2"/>
+      <c r="E509" s="3"/>
+      <c r="F509" s="5">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="510" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A510" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B510" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C510" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D510" s="2"/>
+      <c r="E510" s="3"/>
+      <c r="F510" s="5">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="511" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A511" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B511" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C511" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D511" s="2"/>
+      <c r="E511" s="3"/>
+      <c r="F511" s="5">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="512" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A512" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B512" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C512" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D512" s="2"/>
+      <c r="E512" s="3"/>
+      <c r="F512" s="5">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="513" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A513" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B513" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C513" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D513" s="2"/>
+      <c r="E513" s="3"/>
+      <c r="F513" s="5">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="514" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A514" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B514" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C514" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D514" s="2"/>
+      <c r="E514" s="3"/>
+      <c r="F514" s="5">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="515" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A515" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B515" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C515" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D515" s="2"/>
+      <c r="E515" s="3"/>
+      <c r="F515" s="5">
+        <v>46267</v>
+      </c>
+    </row>
+    <row r="516" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A516" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B516" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C516" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D516" s="2"/>
+      <c r="E516" s="3"/>
+      <c r="F516" s="5">
+        <v>46267</v>
+      </c>
+    </row>
+    <row r="517" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A517" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B517" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C517" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D517" s="2"/>
+      <c r="E517" s="3"/>
+      <c r="F517" s="5">
+        <v>46267</v>
+      </c>
+    </row>
+    <row r="518" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A518" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B518" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C518" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D518" s="2"/>
+      <c r="E518" s="3"/>
+      <c r="F518" s="5">
+        <v>46267</v>
+      </c>
+    </row>
+    <row r="519" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A519" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B519" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C519" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D519" s="2"/>
+      <c r="E519" s="3"/>
+      <c r="F519" s="5">
+        <v>46267</v>
+      </c>
+    </row>
+    <row r="520" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A520" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B520" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C520" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D520" s="2"/>
+      <c r="E520" s="3"/>
+      <c r="F520" s="5">
+        <v>46267</v>
+      </c>
+    </row>
+    <row r="521" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A521" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B521" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C521" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D521" s="2"/>
+      <c r="E521" s="3"/>
+      <c r="F521" s="5">
+        <v>46267</v>
+      </c>
+    </row>
+    <row r="522" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A522" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B522" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C522" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D522" s="2"/>
+      <c r="E522" s="3"/>
+      <c r="F522" s="5">
+        <v>46267</v>
+      </c>
+    </row>
+    <row r="523" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A523" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B523" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C523" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D523" s="2"/>
+      <c r="E523" s="3"/>
+      <c r="F523" s="5">
+        <v>46267</v>
+      </c>
+    </row>
+    <row r="524" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A524" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B524" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C524" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D524" s="2"/>
+      <c r="E524" s="3"/>
+      <c r="F524" s="5">
+        <v>46267</v>
+      </c>
+    </row>
+    <row r="525" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A525" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B525" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C525" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D525" s="2"/>
+      <c r="E525" s="3"/>
+      <c r="F525" s="5">
+        <v>46268</v>
+      </c>
+    </row>
+    <row r="526" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A526" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B526" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C526" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D526" s="2"/>
+      <c r="E526" s="3"/>
+      <c r="F526" s="5">
+        <v>46268</v>
+      </c>
+    </row>
+    <row r="527" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A527" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B527" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C527" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D527" s="2"/>
+      <c r="E527" s="3"/>
+      <c r="F527" s="5">
+        <v>46268</v>
+      </c>
+    </row>
+    <row r="528" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A528" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B528" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C528" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D528" s="2"/>
+      <c r="E528" s="3"/>
+      <c r="F528" s="5">
+        <v>46268</v>
+      </c>
+    </row>
+    <row r="529" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A529" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B529" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C529" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D529" s="2"/>
+      <c r="E529" s="3"/>
+      <c r="F529" s="5">
+        <v>46268</v>
+      </c>
+    </row>
+    <row r="530" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A530" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B530" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C530" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D530" s="2"/>
+      <c r="E530" s="3"/>
+      <c r="F530" s="5">
+        <v>46268</v>
+      </c>
+    </row>
+    <row r="531" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A531" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B531" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C531" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D531" s="2"/>
+      <c r="E531" s="3"/>
+      <c r="F531" s="5">
+        <v>46268</v>
+      </c>
+    </row>
+    <row r="532" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A532" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B532" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C532" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D532" s="2"/>
+      <c r="E532" s="3"/>
+      <c r="F532" s="5">
+        <v>46268</v>
+      </c>
+    </row>
+    <row r="533" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A533" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B533" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C533" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D533" s="2"/>
+      <c r="E533" s="3"/>
+      <c r="F533" s="5">
+        <v>46268</v>
+      </c>
+    </row>
+    <row r="534" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A534" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B534" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C534" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D534" s="2"/>
+      <c r="E534" s="3"/>
+      <c r="F534" s="5">
+        <v>46268</v>
+      </c>
+    </row>
+    <row r="535" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A535" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B535" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C535" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D535" s="2"/>
+      <c r="E535" s="3"/>
+      <c r="F535" s="5">
+        <v>46269</v>
+      </c>
+    </row>
+    <row r="536" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A536" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B536" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C536" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D536" s="2"/>
+      <c r="E536" s="3"/>
+      <c r="F536" s="5">
+        <v>46269</v>
+      </c>
+    </row>
+    <row r="537" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A537" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B537" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C537" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D537" s="2"/>
+      <c r="E537" s="3"/>
+      <c r="F537" s="5">
+        <v>46269</v>
+      </c>
+    </row>
+    <row r="538" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A538" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B538" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C538" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D538" s="2"/>
+      <c r="E538" s="3"/>
+      <c r="F538" s="5">
+        <v>46269</v>
+      </c>
+    </row>
+    <row r="539" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A539" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B539" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C539" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D539" s="2"/>
+      <c r="E539" s="3"/>
+      <c r="F539" s="5">
+        <v>46269</v>
+      </c>
+    </row>
+    <row r="540" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A540" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B540" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C540" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D540" s="2"/>
+      <c r="E540" s="3"/>
+      <c r="F540" s="5">
+        <v>46269</v>
+      </c>
+    </row>
+    <row r="541" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A541" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B541" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C541" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D541" s="2"/>
+      <c r="E541" s="3"/>
+      <c r="F541" s="5">
+        <v>46269</v>
+      </c>
+    </row>
+    <row r="542" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A542" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B542" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C542" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D542" s="2"/>
+      <c r="E542" s="3"/>
+      <c r="F542" s="5">
+        <v>46269</v>
+      </c>
+    </row>
+    <row r="543" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A543" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B543" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C543" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D543" s="2"/>
+      <c r="E543" s="3"/>
+      <c r="F543" s="5">
+        <v>46269</v>
+      </c>
+    </row>
+    <row r="544" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A544" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B544" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C544" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D544" s="2"/>
+      <c r="E544" s="3"/>
+      <c r="F544" s="5">
+        <v>46269</v>
+      </c>
+    </row>
+    <row r="545" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A545" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B545" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C545" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D545" s="2"/>
+      <c r="E545" s="3"/>
+      <c r="F545" s="5">
+        <v>46270</v>
+      </c>
+    </row>
+    <row r="546" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A546" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B546" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C546" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D546" s="2"/>
+      <c r="E546" s="3"/>
+      <c r="F546" s="5">
+        <v>46270</v>
+      </c>
+    </row>
+    <row r="547" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A547" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B547" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C547" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D547" s="2"/>
+      <c r="E547" s="3"/>
+      <c r="F547" s="5">
+        <v>46270</v>
+      </c>
+    </row>
+    <row r="548" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A548" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B548" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C548" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D548" s="2"/>
+      <c r="E548" s="3"/>
+      <c r="F548" s="5">
+        <v>46270</v>
+      </c>
+    </row>
+    <row r="549" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A549" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B549" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C549" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D549" s="2"/>
+      <c r="E549" s="3"/>
+      <c r="F549" s="5">
+        <v>46270</v>
+      </c>
+    </row>
+    <row r="550" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A550" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B550" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C550" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D550" s="2"/>
+      <c r="E550" s="3"/>
+      <c r="F550" s="5">
+        <v>46270</v>
+      </c>
+    </row>
+    <row r="551" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A551" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B551" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C551" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D551" s="2"/>
+      <c r="E551" s="3"/>
+      <c r="F551" s="5">
+        <v>46270</v>
+      </c>
+    </row>
+    <row r="552" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A552" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B552" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C552" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D552" s="2"/>
+      <c r="E552" s="3"/>
+      <c r="F552" s="5">
+        <v>46270</v>
+      </c>
+    </row>
+    <row r="553" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A553" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B553" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C553" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D553" s="2"/>
+      <c r="E553" s="3"/>
+      <c r="F553" s="5">
+        <v>46270</v>
+      </c>
+    </row>
+    <row r="554" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A554" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B554" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C554" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D554" s="2"/>
+      <c r="E554" s="3"/>
+      <c r="F554" s="5">
+        <v>46270</v>
+      </c>
+    </row>
+    <row r="555" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A555" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B555" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C555" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D555" s="2"/>
+      <c r="E555" s="3"/>
+      <c r="F555" s="5">
+        <v>46272</v>
+      </c>
+    </row>
+    <row r="556" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A556" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B556" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C556" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D556" s="2"/>
+      <c r="E556" s="3"/>
+      <c r="F556" s="5">
+        <v>46272</v>
+      </c>
+    </row>
+    <row r="557" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A557" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B557" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C557" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D557" s="2"/>
+      <c r="E557" s="3"/>
+      <c r="F557" s="5">
+        <v>46272</v>
+      </c>
+    </row>
+    <row r="558" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A558" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B558" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C558" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D558" s="2"/>
+      <c r="E558" s="3"/>
+      <c r="F558" s="5">
+        <v>46272</v>
+      </c>
+    </row>
+    <row r="559" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A559" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B559" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C559" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D559" s="2"/>
+      <c r="E559" s="3"/>
+      <c r="F559" s="5">
+        <v>46272</v>
+      </c>
+    </row>
+    <row r="560" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A560" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B560" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C560" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D560" s="2"/>
+      <c r="E560" s="3"/>
+      <c r="F560" s="5">
+        <v>46272</v>
+      </c>
+    </row>
+    <row r="561" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A561" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B561" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C561" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D561" s="2"/>
+      <c r="E561" s="3"/>
+      <c r="F561" s="5">
+        <v>46272</v>
+      </c>
+    </row>
+    <row r="562" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A562" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B562" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C562" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D562" s="2"/>
+      <c r="E562" s="3"/>
+      <c r="F562" s="5">
+        <v>46272</v>
+      </c>
+    </row>
+    <row r="563" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A563" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B563" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C563" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D563" s="2"/>
+      <c r="E563" s="3"/>
+      <c r="F563" s="5">
+        <v>46272</v>
+      </c>
+    </row>
+    <row r="564" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A564" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B564" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C564" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D564" s="2"/>
+      <c r="E564" s="3"/>
+      <c r="F564" s="5">
+        <v>46272</v>
+      </c>
+    </row>
+    <row r="565" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A565" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B565" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C565" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D565" s="2"/>
+      <c r="E565" s="3"/>
+      <c r="F565" s="5">
+        <v>46273</v>
+      </c>
+    </row>
+    <row r="566" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A566" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B566" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C566" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D566" s="2"/>
+      <c r="E566" s="3"/>
+      <c r="F566" s="5">
+        <v>46273</v>
+      </c>
+    </row>
+    <row r="567" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A567" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B567" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C567" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D567" s="2"/>
+      <c r="E567" s="3"/>
+      <c r="F567" s="5">
+        <v>46273</v>
+      </c>
+    </row>
+    <row r="568" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A568" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B568" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C568" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D568" s="2"/>
+      <c r="E568" s="3"/>
+      <c r="F568" s="5">
+        <v>46273</v>
+      </c>
+    </row>
+    <row r="569" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A569" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B569" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C569" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D569" s="2"/>
+      <c r="E569" s="3"/>
+      <c r="F569" s="5">
+        <v>46273</v>
+      </c>
+    </row>
+    <row r="570" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A570" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B570" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C570" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D570" s="2"/>
+      <c r="E570" s="3"/>
+      <c r="F570" s="5">
+        <v>46273</v>
+      </c>
+    </row>
+    <row r="571" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A571" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B571" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C571" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D571" s="2"/>
+      <c r="E571" s="3"/>
+      <c r="F571" s="5">
+        <v>46273</v>
+      </c>
+    </row>
+    <row r="572" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A572" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B572" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C572" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D572" s="2"/>
+      <c r="E572" s="3"/>
+      <c r="F572" s="5">
+        <v>46273</v>
+      </c>
+    </row>
+    <row r="573" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A573" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B573" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C573" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D573" s="2"/>
+      <c r="E573" s="3"/>
+      <c r="F573" s="5">
+        <v>46273</v>
+      </c>
+    </row>
+    <row r="574" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A574" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B574" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C574" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D574" s="2"/>
+      <c r="E574" s="3"/>
+      <c r="F574" s="5">
+        <v>46273</v>
+      </c>
+    </row>
+    <row r="575" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A575" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B575" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C575" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D575" s="2"/>
+      <c r="E575" s="3"/>
+      <c r="F575" s="5">
+        <v>46274</v>
+      </c>
+    </row>
+    <row r="576" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A576" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B576" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C576" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D576" s="2"/>
+      <c r="E576" s="3"/>
+      <c r="F576" s="5">
+        <v>46274</v>
+      </c>
+    </row>
+    <row r="577" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A577" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B577" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C577" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D577" s="2"/>
+      <c r="E577" s="3"/>
+      <c r="F577" s="5">
+        <v>46274</v>
+      </c>
+    </row>
+    <row r="578" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A578" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B578" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C578" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D578" s="2"/>
+      <c r="E578" s="3"/>
+      <c r="F578" s="5">
+        <v>46274</v>
+      </c>
+    </row>
+    <row r="579" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A579" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B579" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C579" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D579" s="2"/>
+      <c r="E579" s="3"/>
+      <c r="F579" s="5">
+        <v>46274</v>
+      </c>
+    </row>
+    <row r="580" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A580" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B580" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C580" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D580" s="2"/>
+      <c r="E580" s="3"/>
+      <c r="F580" s="5">
+        <v>46274</v>
+      </c>
+    </row>
+    <row r="581" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A581" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B581" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C581" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D581" s="2"/>
+      <c r="E581" s="3"/>
+      <c r="F581" s="5">
+        <v>46274</v>
+      </c>
+    </row>
+    <row r="582" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A582" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B582" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C582" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D582" s="2"/>
+      <c r="E582" s="3"/>
+      <c r="F582" s="5">
+        <v>46274</v>
+      </c>
+    </row>
+    <row r="583" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A583" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B583" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C583" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D583" s="2"/>
+      <c r="E583" s="3"/>
+      <c r="F583" s="5">
+        <v>46274</v>
+      </c>
+    </row>
+    <row r="584" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A584" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B584" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C584" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D584" s="2"/>
+      <c r="E584" s="3"/>
+      <c r="F584" s="5">
+        <v>46274</v>
+      </c>
+    </row>
+    <row r="585" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A585" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B585" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C585" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D585" s="2"/>
+      <c r="E585" s="3"/>
+      <c r="F585" s="5">
+        <v>46275</v>
+      </c>
+    </row>
+    <row r="586" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A586" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B586" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C586" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D586" s="2"/>
+      <c r="E586" s="3"/>
+      <c r="F586" s="5">
+        <v>46275</v>
+      </c>
+    </row>
+    <row r="587" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A587" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B587" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C587" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D587" s="2"/>
+      <c r="E587" s="3"/>
+      <c r="F587" s="5">
+        <v>46275</v>
+      </c>
+    </row>
+    <row r="588" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A588" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B588" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C588" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D588" s="2"/>
+      <c r="E588" s="3"/>
+      <c r="F588" s="5">
+        <v>46275</v>
+      </c>
+    </row>
+    <row r="589" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A589" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B589" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C589" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D589" s="2"/>
+      <c r="E589" s="3"/>
+      <c r="F589" s="5">
+        <v>46275</v>
+      </c>
+    </row>
+    <row r="590" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A590" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B590" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C590" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D590" s="2"/>
+      <c r="E590" s="3"/>
+      <c r="F590" s="5">
+        <v>46275</v>
+      </c>
+    </row>
+    <row r="591" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A591" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B591" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C591" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D591" s="2"/>
+      <c r="E591" s="3"/>
+      <c r="F591" s="5">
+        <v>46275</v>
+      </c>
+    </row>
+    <row r="592" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A592" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B592" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C592" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D592" s="2"/>
+      <c r="E592" s="3"/>
+      <c r="F592" s="5">
+        <v>46275</v>
+      </c>
+    </row>
+    <row r="593" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A593" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B593" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C593" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D593" s="2"/>
+      <c r="E593" s="3"/>
+      <c r="F593" s="5">
+        <v>46275</v>
+      </c>
+    </row>
+    <row r="594" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A594" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B594" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C594" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D594" s="2"/>
+      <c r="E594" s="3"/>
+      <c r="F594" s="5">
+        <v>46275</v>
+      </c>
+    </row>
+    <row r="595" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A595" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B595" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C595" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D595" s="2"/>
+      <c r="E595" s="3"/>
+      <c r="F595" s="5">
+        <v>46276</v>
+      </c>
+    </row>
+    <row r="596" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A596" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B596" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C596" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D596" s="2"/>
+      <c r="E596" s="3"/>
+      <c r="F596" s="5">
+        <v>46276</v>
+      </c>
+    </row>
+    <row r="597" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A597" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B597" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C597" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D597" s="2"/>
+      <c r="E597" s="3"/>
+      <c r="F597" s="5">
+        <v>46276</v>
+      </c>
+    </row>
+    <row r="598" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A598" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B598" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C598" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D598" s="2"/>
+      <c r="E598" s="3"/>
+      <c r="F598" s="5">
+        <v>46276</v>
+      </c>
+    </row>
+    <row r="599" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A599" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B599" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C599" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D599" s="2"/>
+      <c r="E599" s="3"/>
+      <c r="F599" s="5">
+        <v>46276</v>
+      </c>
+    </row>
+    <row r="600" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A600" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B600" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C600" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D600" s="2"/>
+      <c r="E600" s="3"/>
+      <c r="F600" s="5">
+        <v>46276</v>
+      </c>
+    </row>
+    <row r="601" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A601" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B601" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C601" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D601" s="2"/>
+      <c r="E601" s="3"/>
+      <c r="F601" s="5">
+        <v>46276</v>
+      </c>
+    </row>
+    <row r="602" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A602" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B602" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C602" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D602" s="2"/>
+      <c r="E602" s="3"/>
+      <c r="F602" s="5">
+        <v>46276</v>
+      </c>
+    </row>
+    <row r="603" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A603" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B603" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C603" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D603" s="2"/>
+      <c r="E603" s="3"/>
+      <c r="F603" s="5">
+        <v>46276</v>
+      </c>
+    </row>
+    <row r="604" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A604" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B604" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C604" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D604" s="2"/>
+      <c r="E604" s="3"/>
+      <c r="F604" s="5">
+        <v>46276</v>
+      </c>
+    </row>
+    <row r="605" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A605" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B605" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C605" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D605" s="2"/>
+      <c r="E605" s="3"/>
+      <c r="F605" s="5">
+        <v>46277</v>
+      </c>
+    </row>
+    <row r="606" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A606" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B606" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C606" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D606" s="2"/>
+      <c r="E606" s="3"/>
+      <c r="F606" s="5">
+        <v>46277</v>
+      </c>
+    </row>
+    <row r="607" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A607" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B607" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C607" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D607" s="2"/>
+      <c r="E607" s="3"/>
+      <c r="F607" s="5">
+        <v>46277</v>
+      </c>
+    </row>
+    <row r="608" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A608" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B608" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C608" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D608" s="2"/>
+      <c r="E608" s="3"/>
+      <c r="F608" s="5">
+        <v>46277</v>
+      </c>
+    </row>
+    <row r="609" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A609" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B609" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C609" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D609" s="2"/>
+      <c r="E609" s="3"/>
+      <c r="F609" s="5">
+        <v>46277</v>
+      </c>
+    </row>
+    <row r="610" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A610" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B610" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C610" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D610" s="2"/>
+      <c r="E610" s="3"/>
+      <c r="F610" s="5">
+        <v>46277</v>
+      </c>
+    </row>
+    <row r="611" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A611" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B611" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C611" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D611" s="2"/>
+      <c r="E611" s="3"/>
+      <c r="F611" s="5">
+        <v>46277</v>
+      </c>
+    </row>
+    <row r="612" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A612" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B612" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C612" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D612" s="2"/>
+      <c r="E612" s="3"/>
+      <c r="F612" s="5">
+        <v>46277</v>
+      </c>
+    </row>
+    <row r="613" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A613" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B613" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C613" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D613" s="2"/>
+      <c r="E613" s="3"/>
+      <c r="F613" s="5">
+        <v>46277</v>
+      </c>
+    </row>
+    <row r="614" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A614" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B614" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C614" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D614" s="2"/>
+      <c r="E614" s="3"/>
+      <c r="F614" s="5">
+        <v>46277</v>
+      </c>
+    </row>
+    <row r="615" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A615" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B615" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C615" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D615" s="2"/>
+      <c r="E615" s="3"/>
+      <c r="F615" s="5">
+        <v>46279</v>
+      </c>
+    </row>
+    <row r="616" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A616" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B616" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C616" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D616" s="2"/>
+      <c r="E616" s="3"/>
+      <c r="F616" s="5">
+        <v>46279</v>
+      </c>
+    </row>
+    <row r="617" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A617" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B617" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C617" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D617" s="2"/>
+      <c r="E617" s="3"/>
+      <c r="F617" s="5">
+        <v>46279</v>
+      </c>
+    </row>
+    <row r="618" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A618" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B618" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C618" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D618" s="2"/>
+      <c r="E618" s="3"/>
+      <c r="F618" s="5">
+        <v>46279</v>
+      </c>
+    </row>
+    <row r="619" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A619" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B619" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C619" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D619" s="2"/>
+      <c r="E619" s="3"/>
+      <c r="F619" s="5">
+        <v>46279</v>
+      </c>
+    </row>
+    <row r="620" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A620" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B620" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C620" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D620" s="2"/>
+      <c r="E620" s="3"/>
+      <c r="F620" s="5">
+        <v>46279</v>
+      </c>
+    </row>
+    <row r="621" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A621" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B621" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C621" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D621" s="2"/>
+      <c r="E621" s="3"/>
+      <c r="F621" s="5">
+        <v>46279</v>
+      </c>
+    </row>
+    <row r="622" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A622" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B622" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C622" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D622" s="2"/>
+      <c r="E622" s="3"/>
+      <c r="F622" s="5">
+        <v>46279</v>
+      </c>
+    </row>
+    <row r="623" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A623" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B623" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C623" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D623" s="2"/>
+      <c r="E623" s="3"/>
+      <c r="F623" s="5">
+        <v>46279</v>
+      </c>
+    </row>
+    <row r="624" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A624" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B624" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C624" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D624" s="2"/>
+      <c r="E624" s="3"/>
+      <c r="F624" s="5">
+        <v>46279</v>
+      </c>
+    </row>
+    <row r="625" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A625" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B625" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C625" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D625" s="2"/>
+      <c r="E625" s="3"/>
+      <c r="F625" s="5">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="626" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A626" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B626" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C626" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D626" s="2"/>
+      <c r="E626" s="3"/>
+      <c r="F626" s="5">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="627" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A627" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B627" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C627" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D627" s="2"/>
+      <c r="E627" s="3"/>
+      <c r="F627" s="5">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="628" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A628" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B628" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C628" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D628" s="2"/>
+      <c r="E628" s="3"/>
+      <c r="F628" s="5">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="629" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A629" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B629" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C629" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D629" s="2"/>
+      <c r="E629" s="3"/>
+      <c r="F629" s="5">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="630" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A630" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B630" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C630" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D630" s="2"/>
+      <c r="E630" s="3"/>
+      <c r="F630" s="5">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="631" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A631" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B631" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C631" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D631" s="2"/>
+      <c r="E631" s="3"/>
+      <c r="F631" s="5">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="632" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A632" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B632" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C632" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D632" s="2"/>
+      <c r="E632" s="3"/>
+      <c r="F632" s="5">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="633" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A633" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B633" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C633" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D633" s="2"/>
+      <c r="E633" s="3"/>
+      <c r="F633" s="5">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="634" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A634" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B634" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C634" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D634" s="2"/>
+      <c r="E634" s="3"/>
+      <c r="F634" s="5">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="635" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A635" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B635" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C635" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D635" s="2"/>
+      <c r="E635" s="3"/>
+      <c r="F635" s="5">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="636" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A636" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B636" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C636" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D636" s="2"/>
+      <c r="E636" s="3"/>
+      <c r="F636" s="5">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="637" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A637" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B637" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C637" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D637" s="2"/>
+      <c r="E637" s="3"/>
+      <c r="F637" s="5">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="638" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A638" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B638" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C638" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D638" s="2"/>
+      <c r="E638" s="3"/>
+      <c r="F638" s="5">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="639" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A639" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B639" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C639" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D639" s="2"/>
+      <c r="E639" s="3"/>
+      <c r="F639" s="5">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="640" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A640" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B640" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C640" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D640" s="2"/>
+      <c r="E640" s="3"/>
+      <c r="F640" s="5">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="641" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A641" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B641" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C641" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D641" s="2"/>
+      <c r="E641" s="3"/>
+      <c r="F641" s="5">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="642" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A642" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B642" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C642" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D642" s="2"/>
+      <c r="E642" s="3"/>
+      <c r="F642" s="5">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="643" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A643" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B643" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C643" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D643" s="2"/>
+      <c r="E643" s="3"/>
+      <c r="F643" s="5">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="644" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A644" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B644" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C644" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D644" s="2"/>
+      <c r="E644" s="3"/>
+      <c r="F644" s="5">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="645" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A645" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B645" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C645" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D645" s="2"/>
+      <c r="E645" s="3"/>
+      <c r="F645" s="5">
+        <v>46282</v>
+      </c>
+    </row>
+    <row r="646" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A646" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B646" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C646" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D646" s="2"/>
+      <c r="E646" s="3"/>
+      <c r="F646" s="5">
+        <v>46282</v>
+      </c>
+    </row>
+    <row r="647" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A647" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B647" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C647" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D647" s="2"/>
+      <c r="E647" s="3"/>
+      <c r="F647" s="5">
+        <v>46282</v>
+      </c>
+    </row>
+    <row r="648" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A648" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B648" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C648" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D648" s="2"/>
+      <c r="E648" s="3"/>
+      <c r="F648" s="5">
+        <v>46282</v>
+      </c>
+    </row>
+    <row r="649" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A649" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B649" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C649" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D649" s="2"/>
+      <c r="E649" s="3"/>
+      <c r="F649" s="5">
+        <v>46282</v>
+      </c>
+    </row>
+    <row r="650" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A650" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B650" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C650" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D650" s="2"/>
+      <c r="E650" s="3"/>
+      <c r="F650" s="5">
+        <v>46282</v>
+      </c>
+    </row>
+    <row r="651" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A651" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B651" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C651" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D651" s="2"/>
+      <c r="E651" s="3"/>
+      <c r="F651" s="5">
+        <v>46282</v>
+      </c>
+    </row>
+    <row r="652" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A652" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B652" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C652" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D652" s="2"/>
+      <c r="E652" s="3"/>
+      <c r="F652" s="5">
+        <v>46282</v>
+      </c>
+    </row>
+    <row r="653" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A653" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B653" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C653" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D653" s="2"/>
+      <c r="E653" s="3"/>
+      <c r="F653" s="5">
+        <v>46282</v>
+      </c>
+    </row>
+    <row r="654" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A654" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B654" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C654" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D654" s="2"/>
+      <c r="E654" s="3"/>
+      <c r="F654" s="5">
+        <v>46282</v>
+      </c>
+    </row>
+    <row r="655" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A655" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B655" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C655" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D655" s="2"/>
+      <c r="E655" s="3"/>
+      <c r="F655" s="5">
+        <v>46283</v>
+      </c>
+    </row>
+    <row r="656" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A656" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B656" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C656" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D656" s="2"/>
+      <c r="E656" s="3"/>
+      <c r="F656" s="5">
+        <v>46283</v>
+      </c>
+    </row>
+    <row r="657" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A657" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B657" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C657" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D657" s="2"/>
+      <c r="E657" s="3"/>
+      <c r="F657" s="5">
+        <v>46283</v>
+      </c>
+    </row>
+    <row r="658" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A658" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B658" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C658" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D658" s="2"/>
+      <c r="E658" s="3"/>
+      <c r="F658" s="5">
+        <v>46283</v>
+      </c>
+    </row>
+    <row r="659" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A659" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B659" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C659" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D659" s="2"/>
+      <c r="E659" s="3"/>
+      <c r="F659" s="5">
+        <v>46283</v>
+      </c>
+    </row>
+    <row r="660" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A660" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B660" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C660" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D660" s="2"/>
+      <c r="E660" s="3"/>
+      <c r="F660" s="5">
+        <v>46283</v>
+      </c>
+    </row>
+    <row r="661" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A661" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B661" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C661" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D661" s="2"/>
+      <c r="E661" s="3"/>
+      <c r="F661" s="5">
+        <v>46283</v>
+      </c>
+    </row>
+    <row r="662" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A662" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B662" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C662" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D662" s="2"/>
+      <c r="E662" s="3"/>
+      <c r="F662" s="5">
+        <v>46283</v>
+      </c>
+    </row>
+    <row r="663" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A663" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B663" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C663" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D663" s="2"/>
+      <c r="E663" s="3"/>
+      <c r="F663" s="5">
+        <v>46283</v>
+      </c>
+    </row>
+    <row r="664" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A664" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B664" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C664" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D664" s="2"/>
+      <c r="E664" s="3"/>
+      <c r="F664" s="5">
+        <v>46283</v>
+      </c>
+    </row>
+    <row r="665" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A665" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B665" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C665" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D665" s="2"/>
+      <c r="E665" s="3"/>
+      <c r="F665" s="5">
+        <v>46284</v>
+      </c>
+    </row>
+    <row r="666" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A666" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B666" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C666" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D666" s="2"/>
+      <c r="E666" s="3"/>
+      <c r="F666" s="5">
+        <v>46284</v>
+      </c>
+    </row>
+    <row r="667" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A667" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B667" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C667" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D667" s="2"/>
+      <c r="E667" s="3"/>
+      <c r="F667" s="5">
+        <v>46284</v>
+      </c>
+    </row>
+    <row r="668" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A668" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B668" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C668" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D668" s="2"/>
+      <c r="E668" s="3"/>
+      <c r="F668" s="5">
+        <v>46284</v>
+      </c>
+    </row>
+    <row r="669" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A669" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B669" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C669" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D669" s="2"/>
+      <c r="E669" s="3"/>
+      <c r="F669" s="5">
+        <v>46284</v>
+      </c>
+    </row>
+    <row r="670" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A670" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B670" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C670" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D670" s="2"/>
+      <c r="E670" s="3"/>
+      <c r="F670" s="5">
+        <v>46284</v>
+      </c>
+    </row>
+    <row r="671" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A671" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B671" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C671" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D671" s="2"/>
+      <c r="E671" s="3"/>
+      <c r="F671" s="5">
+        <v>46284</v>
+      </c>
+    </row>
+    <row r="672" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A672" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B672" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C672" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D672" s="2"/>
+      <c r="E672" s="3"/>
+      <c r="F672" s="5">
+        <v>46284</v>
+      </c>
+    </row>
+    <row r="673" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A673" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B673" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C673" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D673" s="2"/>
+      <c r="E673" s="3"/>
+      <c r="F673" s="5">
+        <v>46284</v>
+      </c>
+    </row>
+    <row r="674" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A674" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B674" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C674" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D674" s="2"/>
+      <c r="E674" s="3"/>
+      <c r="F674" s="5">
+        <v>46284</v>
+      </c>
+    </row>
+    <row r="675" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A675" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B675" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C675" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D675" s="2"/>
+      <c r="E675" s="3"/>
+      <c r="F675" s="5">
+        <v>46286</v>
+      </c>
+    </row>
+    <row r="676" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A676" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B676" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C676" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D676" s="2"/>
+      <c r="E676" s="3"/>
+      <c r="F676" s="5">
+        <v>46286</v>
+      </c>
+    </row>
+    <row r="677" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A677" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B677" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C677" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D677" s="2"/>
+      <c r="E677" s="3"/>
+      <c r="F677" s="5">
+        <v>46286</v>
+      </c>
+    </row>
+    <row r="678" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A678" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B678" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C678" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D678" s="2"/>
+      <c r="E678" s="3"/>
+      <c r="F678" s="5">
+        <v>46286</v>
+      </c>
+    </row>
+    <row r="679" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A679" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B679" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C679" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D679" s="2"/>
+      <c r="E679" s="3"/>
+      <c r="F679" s="5">
+        <v>46286</v>
+      </c>
+    </row>
+    <row r="680" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A680" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B680" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C680" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D680" s="2"/>
+      <c r="E680" s="3"/>
+      <c r="F680" s="5">
+        <v>46286</v>
+      </c>
+    </row>
+    <row r="681" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A681" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B681" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C681" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D681" s="2"/>
+      <c r="E681" s="3"/>
+      <c r="F681" s="5">
+        <v>46286</v>
+      </c>
+    </row>
+    <row r="682" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A682" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B682" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C682" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D682" s="2"/>
+      <c r="E682" s="3"/>
+      <c r="F682" s="5">
+        <v>46286</v>
+      </c>
+    </row>
+    <row r="683" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A683" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B683" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C683" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D683" s="2"/>
+      <c r="E683" s="3"/>
+      <c r="F683" s="5">
+        <v>46286</v>
+      </c>
+    </row>
+    <row r="684" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A684" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B684" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C684" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D684" s="2"/>
+      <c r="E684" s="3"/>
+      <c r="F684" s="5">
+        <v>46286</v>
+      </c>
+    </row>
+    <row r="685" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A685" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B685" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C685" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D685" s="2"/>
+      <c r="E685" s="3"/>
+      <c r="F685" s="5">
+        <v>46287</v>
+      </c>
+    </row>
+    <row r="686" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A686" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B686" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C686" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D686" s="2"/>
+      <c r="E686" s="3"/>
+      <c r="F686" s="5">
+        <v>46287</v>
+      </c>
+    </row>
+    <row r="687" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A687" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B687" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C687" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D687" s="2"/>
+      <c r="E687" s="3"/>
+      <c r="F687" s="5">
+        <v>46287</v>
+      </c>
+    </row>
+    <row r="688" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A688" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B688" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C688" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D688" s="2"/>
+      <c r="E688" s="3"/>
+      <c r="F688" s="5">
+        <v>46287</v>
+      </c>
+    </row>
+    <row r="689" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A689" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B689" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C689" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D689" s="2"/>
+      <c r="E689" s="3"/>
+      <c r="F689" s="5">
+        <v>46287</v>
+      </c>
+    </row>
+    <row r="690" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A690" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B690" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C690" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D690" s="2"/>
+      <c r="E690" s="3"/>
+      <c r="F690" s="5">
+        <v>46287</v>
+      </c>
+    </row>
+    <row r="691" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A691" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B691" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C691" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D691" s="2"/>
+      <c r="E691" s="3"/>
+      <c r="F691" s="5">
+        <v>46287</v>
+      </c>
+    </row>
+    <row r="692" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A692" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B692" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C692" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D692" s="2"/>
+      <c r="E692" s="3"/>
+      <c r="F692" s="5">
+        <v>46287</v>
+      </c>
+    </row>
+    <row r="693" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A693" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B693" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C693" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D693" s="2"/>
+      <c r="E693" s="3"/>
+      <c r="F693" s="5">
+        <v>46287</v>
+      </c>
+    </row>
+    <row r="694" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A694" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B694" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C694" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D694" s="2"/>
+      <c r="E694" s="3"/>
+      <c r="F694" s="5">
+        <v>46287</v>
+      </c>
+    </row>
+    <row r="695" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A695" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B695" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C695" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D695" s="2"/>
+      <c r="E695" s="3"/>
+      <c r="F695" s="5">
+        <v>46288</v>
+      </c>
+    </row>
+    <row r="696" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A696" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B696" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C696" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D696" s="2"/>
+      <c r="E696" s="3"/>
+      <c r="F696" s="5">
+        <v>46288</v>
+      </c>
+    </row>
+    <row r="697" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A697" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B697" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C697" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D697" s="2"/>
+      <c r="E697" s="3"/>
+      <c r="F697" s="5">
+        <v>46288</v>
+      </c>
+    </row>
+    <row r="698" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A698" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B698" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C698" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D698" s="2"/>
+      <c r="E698" s="3"/>
+      <c r="F698" s="5">
+        <v>46288</v>
+      </c>
+    </row>
+    <row r="699" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A699" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B699" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C699" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D699" s="2"/>
+      <c r="E699" s="3"/>
+      <c r="F699" s="5">
+        <v>46288</v>
+      </c>
+    </row>
+    <row r="700" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A700" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B700" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C700" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D700" s="2"/>
+      <c r="E700" s="3"/>
+      <c r="F700" s="5">
+        <v>46288</v>
+      </c>
+    </row>
+    <row r="701" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A701" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B701" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C701" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D701" s="2"/>
+      <c r="E701" s="3"/>
+      <c r="F701" s="5">
+        <v>46288</v>
+      </c>
+    </row>
+    <row r="702" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A702" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B702" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C702" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D702" s="2"/>
+      <c r="E702" s="3"/>
+      <c r="F702" s="5">
+        <v>46288</v>
+      </c>
+    </row>
+    <row r="703" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A703" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B703" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C703" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D703" s="2"/>
+      <c r="E703" s="3"/>
+      <c r="F703" s="5">
+        <v>46288</v>
+      </c>
+    </row>
+    <row r="704" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A704" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B704" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C704" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D704" s="2"/>
+      <c r="E704" s="3"/>
+      <c r="F704" s="5">
+        <v>46288</v>
+      </c>
+    </row>
+    <row r="705" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A705" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B705" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C705" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D705" s="2"/>
+      <c r="E705" s="3"/>
+      <c r="F705" s="5">
+        <v>46289</v>
+      </c>
+    </row>
+    <row r="706" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A706" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B706" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C706" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D706" s="2"/>
+      <c r="E706" s="3"/>
+      <c r="F706" s="5">
+        <v>46289</v>
+      </c>
+    </row>
+    <row r="707" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A707" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B707" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C707" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D707" s="2"/>
+      <c r="E707" s="3"/>
+      <c r="F707" s="5">
+        <v>46289</v>
+      </c>
+    </row>
+    <row r="708" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A708" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B708" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C708" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D708" s="2"/>
+      <c r="E708" s="3"/>
+      <c r="F708" s="5">
+        <v>46289</v>
+      </c>
+    </row>
+    <row r="709" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A709" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B709" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C709" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D709" s="2"/>
+      <c r="E709" s="3"/>
+      <c r="F709" s="5">
+        <v>46289</v>
+      </c>
+    </row>
+    <row r="710" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A710" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B710" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C710" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D710" s="2"/>
+      <c r="E710" s="3"/>
+      <c r="F710" s="5">
+        <v>46289</v>
+      </c>
+    </row>
+    <row r="711" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A711" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B711" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C711" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D711" s="2"/>
+      <c r="E711" s="3"/>
+      <c r="F711" s="5">
+        <v>46289</v>
+      </c>
+    </row>
+    <row r="712" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A712" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B712" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C712" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D712" s="2"/>
+      <c r="E712" s="3"/>
+      <c r="F712" s="5">
+        <v>46289</v>
+      </c>
+    </row>
+    <row r="713" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A713" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B713" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C713" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D713" s="2"/>
+      <c r="E713" s="3"/>
+      <c r="F713" s="5">
+        <v>46289</v>
+      </c>
+    </row>
+    <row r="714" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A714" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B714" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C714" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D714" s="2"/>
+      <c r="E714" s="3"/>
+      <c r="F714" s="5">
+        <v>46289</v>
+      </c>
+    </row>
+    <row r="715" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A715" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B715" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C715" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D715" s="2"/>
+      <c r="E715" s="3"/>
+      <c r="F715" s="5">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="716" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A716" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B716" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C716" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D716" s="2"/>
+      <c r="E716" s="3"/>
+      <c r="F716" s="5">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="717" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A717" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B717" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C717" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D717" s="2"/>
+      <c r="E717" s="3"/>
+      <c r="F717" s="5">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="718" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A718" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B718" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C718" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D718" s="2"/>
+      <c r="E718" s="3"/>
+      <c r="F718" s="5">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="719" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A719" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B719" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C719" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D719" s="2"/>
+      <c r="E719" s="3"/>
+      <c r="F719" s="5">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="720" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A720" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B720" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C720" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D720" s="2"/>
+      <c r="E720" s="3"/>
+      <c r="F720" s="5">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="721" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A721" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B721" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C721" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D721" s="2"/>
+      <c r="E721" s="3"/>
+      <c r="F721" s="5">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="722" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A722" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B722" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C722" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D722" s="2"/>
+      <c r="E722" s="3"/>
+      <c r="F722" s="5">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="723" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A723" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B723" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C723" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D723" s="2"/>
+      <c r="E723" s="3"/>
+      <c r="F723" s="5">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="724" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A724" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B724" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C724" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D724" s="2"/>
+      <c r="E724" s="3"/>
+      <c r="F724" s="5">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="725" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A725" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B725" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C725" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D725" s="2"/>
+      <c r="E725" s="3"/>
+      <c r="F725" s="5">
+        <v>46291</v>
+      </c>
+    </row>
+    <row r="726" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A726" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B726" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C726" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D726" s="2"/>
+      <c r="E726" s="3"/>
+      <c r="F726" s="5">
+        <v>46291</v>
+      </c>
+    </row>
+    <row r="727" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A727" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B727" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C727" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D727" s="2"/>
+      <c r="E727" s="3"/>
+      <c r="F727" s="5">
+        <v>46291</v>
+      </c>
+    </row>
+    <row r="728" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A728" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B728" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C728" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D728" s="2"/>
+      <c r="E728" s="3"/>
+      <c r="F728" s="5">
+        <v>46291</v>
+      </c>
+    </row>
+    <row r="729" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A729" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B729" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C729" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D729" s="2"/>
+      <c r="E729" s="3"/>
+      <c r="F729" s="5">
+        <v>46291</v>
+      </c>
+    </row>
+    <row r="730" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A730" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B730" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C730" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D730" s="2"/>
+      <c r="E730" s="3"/>
+      <c r="F730" s="5">
+        <v>46291</v>
+      </c>
+    </row>
+    <row r="731" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A731" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B731" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C731" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D731" s="2"/>
+      <c r="E731" s="3"/>
+      <c r="F731" s="5">
+        <v>46291</v>
+      </c>
+    </row>
+    <row r="732" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A732" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B732" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C732" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D732" s="2"/>
+      <c r="E732" s="3"/>
+      <c r="F732" s="5">
+        <v>46291</v>
+      </c>
+    </row>
+    <row r="733" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A733" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B733" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C733" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D733" s="2"/>
+      <c r="E733" s="3"/>
+      <c r="F733" s="5">
+        <v>46291</v>
+      </c>
+    </row>
+    <row r="734" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A734" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B734" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C734" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D734" s="2"/>
+      <c r="E734" s="3"/>
+      <c r="F734" s="5">
+        <v>46291</v>
+      </c>
+    </row>
+    <row r="735" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A735" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B735" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C735" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D735" s="2"/>
+      <c r="E735" s="3"/>
+      <c r="F735" s="5">
+        <v>46293</v>
+      </c>
+    </row>
+    <row r="736" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A736" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B736" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C736" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D736" s="2"/>
+      <c r="E736" s="3"/>
+      <c r="F736" s="5">
+        <v>46293</v>
+      </c>
+    </row>
+    <row r="737" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A737" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B737" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C737" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D737" s="2"/>
+      <c r="E737" s="3"/>
+      <c r="F737" s="5">
+        <v>46293</v>
+      </c>
+    </row>
+    <row r="738" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A738" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B738" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C738" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D738" s="2"/>
+      <c r="E738" s="3"/>
+      <c r="F738" s="5">
+        <v>46293</v>
+      </c>
+    </row>
+    <row r="739" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A739" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B739" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C739" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D739" s="2"/>
+      <c r="E739" s="3"/>
+      <c r="F739" s="5">
+        <v>46293</v>
+      </c>
+    </row>
+    <row r="740" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A740" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B740" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C740" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D740" s="2"/>
+      <c r="E740" s="3"/>
+      <c r="F740" s="5">
+        <v>46293</v>
+      </c>
+    </row>
+    <row r="741" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A741" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B741" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C741" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D741" s="2"/>
+      <c r="E741" s="3"/>
+      <c r="F741" s="5">
+        <v>46293</v>
+      </c>
+    </row>
+    <row r="742" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A742" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B742" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C742" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D742" s="2"/>
+      <c r="E742" s="3"/>
+      <c r="F742" s="5">
+        <v>46293</v>
+      </c>
+    </row>
+    <row r="743" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A743" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B743" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C743" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D743" s="2"/>
+      <c r="E743" s="3"/>
+      <c r="F743" s="5">
+        <v>46293</v>
+      </c>
+    </row>
+    <row r="744" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A744" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B744" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C744" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D744" s="2"/>
+      <c r="E744" s="3"/>
+      <c r="F744" s="5">
+        <v>46293</v>
+      </c>
+    </row>
+    <row r="745" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A745" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B745" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C745" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D745" s="2"/>
+      <c r="E745" s="3"/>
+      <c r="F745" s="5">
+        <v>46294</v>
+      </c>
+    </row>
+    <row r="746" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A746" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B746" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C746" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D746" s="2"/>
+      <c r="E746" s="3"/>
+      <c r="F746" s="5">
+        <v>46294</v>
+      </c>
+    </row>
+    <row r="747" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A747" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B747" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C747" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D747" s="2"/>
+      <c r="E747" s="3"/>
+      <c r="F747" s="5">
+        <v>46294</v>
+      </c>
+    </row>
+    <row r="748" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A748" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B748" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C748" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D748" s="2"/>
+      <c r="E748" s="3"/>
+      <c r="F748" s="5">
+        <v>46294</v>
+      </c>
+    </row>
+    <row r="749" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A749" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B749" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C749" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D749" s="2"/>
+      <c r="E749" s="3"/>
+      <c r="F749" s="5">
+        <v>46294</v>
+      </c>
+    </row>
+    <row r="750" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A750" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B750" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C750" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D750" s="2"/>
+      <c r="E750" s="3"/>
+      <c r="F750" s="5">
+        <v>46294</v>
+      </c>
+    </row>
+    <row r="751" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A751" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B751" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C751" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D751" s="2"/>
+      <c r="E751" s="3"/>
+      <c r="F751" s="5">
+        <v>46294</v>
+      </c>
+    </row>
+    <row r="752" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A752" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B752" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C752" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D752" s="2"/>
+      <c r="E752" s="3"/>
+      <c r="F752" s="5">
+        <v>46294</v>
+      </c>
+    </row>
+    <row r="753" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A753" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B753" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C753" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D753" s="2"/>
+      <c r="E753" s="3"/>
+      <c r="F753" s="5">
+        <v>46294</v>
+      </c>
+    </row>
+    <row r="754" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A754" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B754" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C754" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D754" s="2"/>
+      <c r="E754" s="3"/>
+      <c r="F754" s="5">
+        <v>46294</v>
+      </c>
+    </row>
+    <row r="755" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A755" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B755" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C755" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D755" s="2"/>
+      <c r="E755" s="3"/>
+      <c r="F755" s="5">
+        <v>46295</v>
+      </c>
+    </row>
+    <row r="756" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A756" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B756" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C756" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D756" s="2"/>
+      <c r="E756" s="3"/>
+      <c r="F756" s="5">
+        <v>46295</v>
+      </c>
+    </row>
+    <row r="757" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A757" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B757" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C757" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D757" s="2"/>
+      <c r="E757" s="3"/>
+      <c r="F757" s="5">
+        <v>46295</v>
+      </c>
+    </row>
+    <row r="758" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A758" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B758" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C758" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D758" s="2"/>
+      <c r="E758" s="3"/>
+      <c r="F758" s="5">
+        <v>46295</v>
+      </c>
+    </row>
+    <row r="759" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A759" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B759" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C759" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D759" s="2"/>
+      <c r="E759" s="3"/>
+      <c r="F759" s="5">
+        <v>46295</v>
+      </c>
+    </row>
+    <row r="760" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A760" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B760" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C760" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D760" s="2"/>
+      <c r="E760" s="3"/>
+      <c r="F760" s="5">
+        <v>46295</v>
+      </c>
+    </row>
+    <row r="761" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A761" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B761" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C761" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D761" s="2"/>
+      <c r="E761" s="3"/>
+      <c r="F761" s="5">
+        <v>46295</v>
+      </c>
+    </row>
+    <row r="762" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A762" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B762" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C762" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D762" s="2"/>
+      <c r="E762" s="3"/>
+      <c r="F762" s="5">
+        <v>46295</v>
+      </c>
+    </row>
+    <row r="763" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A763" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B763" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C763" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D763" s="2"/>
+      <c r="E763" s="3"/>
+      <c r="F763" s="5">
+        <v>46295</v>
+      </c>
+    </row>
+    <row r="764" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A764" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B764" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C764" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D764" s="2"/>
+      <c r="E764" s="3"/>
+      <c r="F764" s="5">
+        <v>46295</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F504" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:F764" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="5">
+      <filters>
+        <dateGroupItem year="2026" month="8" dateTimeGrouping="month"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -12044,13 +16233,14 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <sheetPr>
+  <sheetPr filterMode="1">
     <tabColor rgb="FF2E75B6"/>
   </sheetPr>
-  <dimension ref="A1:AG25"/>
+  <dimension ref="A1:AG34"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="8.85546875" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.42578125" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9" style="6" bestFit="1" customWidth="1"/>
     <col min="3" max="33" width="11.85546875" style="6" bestFit="1" customWidth="1"/>
     <col min="34" max="16384" width="9" style="6"/>
   </cols>
@@ -12156,7 +16346,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>17</v>
       </c>
@@ -12257,7 +16447,7 @@
         <v>46234</v>
       </c>
     </row>
-    <row r="3" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
         <v>17</v>
       </c>
@@ -12342,7 +16532,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>17</v>
       </c>
@@ -12427,7 +16617,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
         <v>17</v>
       </c>
@@ -12512,7 +16702,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>17</v>
       </c>
@@ -12597,7 +16787,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
         <v>17</v>
       </c>
@@ -12682,7 +16872,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
         <v>17</v>
       </c>
@@ -12767,7 +16957,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
         <v>17</v>
       </c>
@@ -12852,7 +17042,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
         <v>17</v>
       </c>
@@ -12937,7 +17127,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
         <v>17</v>
       </c>
@@ -13022,7 +17212,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
         <v>17</v>
       </c>
@@ -13108,10 +17298,10 @@
       </c>
     </row>
     <row r="13" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="9" t="s">
         <v>5</v>
       </c>
       <c r="C13" s="12">
@@ -13209,10 +17399,10 @@
       </c>
     </row>
     <row r="14" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A14" s="9" t="s">
+      <c r="A14" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="B14" s="9" t="s">
+      <c r="B14" s="8" t="s">
         <v>8</v>
       </c>
       <c r="C14" s="15"/>
@@ -13275,7 +17465,7 @@
         <v>5</v>
       </c>
       <c r="AB14" s="8">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AC14" s="8">
         <v>0</v>
@@ -13290,10 +17480,10 @@
       </c>
     </row>
     <row r="15" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A15" s="8" t="s">
+      <c r="A15" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="B15" s="9" t="s">
         <v>10</v>
       </c>
       <c r="C15" s="15"/>
@@ -13356,7 +17546,7 @@
         <v>1</v>
       </c>
       <c r="AB15" s="8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AC15" s="8">
         <v>0</v>
@@ -13371,10 +17561,10 @@
       </c>
     </row>
     <row r="16" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A16" s="9" t="s">
+      <c r="A16" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="B16" s="9" t="s">
+      <c r="B16" s="8" t="s">
         <v>23</v>
       </c>
       <c r="C16" s="15"/>
@@ -13437,7 +17627,7 @@
         <v>2</v>
       </c>
       <c r="AB16" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC16" s="8">
         <v>0</v>
@@ -13452,10 +17642,10 @@
       </c>
     </row>
     <row r="17" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A17" s="8" t="s">
+      <c r="A17" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="B17" s="8" t="s">
+      <c r="B17" s="9" t="s">
         <v>25</v>
       </c>
       <c r="C17" s="15"/>
@@ -13518,7 +17708,7 @@
         <v>1</v>
       </c>
       <c r="AB17" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC17" s="8">
         <v>0</v>
@@ -13533,10 +17723,10 @@
       </c>
     </row>
     <row r="18" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A18" s="9" t="s">
+      <c r="A18" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="B18" s="9" t="s">
+      <c r="B18" s="8" t="s">
         <v>9</v>
       </c>
       <c r="C18" s="15"/>
@@ -13614,10 +17804,10 @@
       </c>
     </row>
     <row r="19" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A19" s="8" t="s">
+      <c r="A19" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="B19" s="8" t="s">
+      <c r="B19" s="9" t="s">
         <v>27</v>
       </c>
       <c r="C19" s="15"/>
@@ -13680,7 +17870,7 @@
         <v>0</v>
       </c>
       <c r="AB19" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC19" s="8">
         <v>0</v>
@@ -13695,10 +17885,10 @@
       </c>
     </row>
     <row r="20" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A20" s="9" t="s">
+      <c r="A20" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="B20" s="9" t="s">
+      <c r="B20" s="8" t="s">
         <v>29</v>
       </c>
       <c r="C20" s="15"/>
@@ -13761,7 +17951,7 @@
         <v>2</v>
       </c>
       <c r="AB20" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC20" s="8">
         <v>0</v>
@@ -13776,10 +17966,10 @@
       </c>
     </row>
     <row r="21" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A21" s="8" t="s">
+      <c r="A21" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="B21" s="8" t="s">
+      <c r="B21" s="9" t="s">
         <v>62</v>
       </c>
       <c r="C21" s="15"/>
@@ -13857,10 +18047,10 @@
       </c>
     </row>
     <row r="22" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A22" s="9" t="s">
+      <c r="A22" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="B22" s="9" t="s">
+      <c r="B22" s="8" t="s">
         <v>13</v>
       </c>
       <c r="C22" s="15"/>
@@ -13923,7 +18113,7 @@
         <v>2</v>
       </c>
       <c r="AB22" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC22" s="8">
         <v>0</v>
@@ -13938,10 +18128,10 @@
       </c>
     </row>
     <row r="23" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A23" s="8" t="s">
+      <c r="A23" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="B23" s="8" t="s">
+      <c r="B23" s="9" t="s">
         <v>67</v>
       </c>
       <c r="C23" s="15"/>
@@ -14004,7 +18194,7 @@
         <v>1</v>
       </c>
       <c r="AB23" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC23" s="8">
         <v>0</v>
@@ -14018,11 +18208,933 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="C25" s="13"/>
+    <row r="24" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C24" s="13">
+        <v>46266</v>
+      </c>
+      <c r="D24" s="13">
+        <v>46267</v>
+      </c>
+      <c r="E24" s="13">
+        <v>46268</v>
+      </c>
+      <c r="F24" s="13">
+        <v>46269</v>
+      </c>
+      <c r="G24" s="14">
+        <v>46270</v>
+      </c>
+      <c r="H24" s="14">
+        <v>46271</v>
+      </c>
+      <c r="I24" s="13">
+        <v>46272</v>
+      </c>
+      <c r="J24" s="13">
+        <v>46273</v>
+      </c>
+      <c r="K24" s="13">
+        <v>46274</v>
+      </c>
+      <c r="L24" s="13">
+        <v>46275</v>
+      </c>
+      <c r="M24" s="13">
+        <v>46276</v>
+      </c>
+      <c r="N24" s="14">
+        <v>46277</v>
+      </c>
+      <c r="O24" s="14">
+        <v>46278</v>
+      </c>
+      <c r="P24" s="13">
+        <v>46279</v>
+      </c>
+      <c r="Q24" s="13">
+        <v>46280</v>
+      </c>
+      <c r="R24" s="13">
+        <v>46281</v>
+      </c>
+      <c r="S24" s="13">
+        <v>46282</v>
+      </c>
+      <c r="T24" s="13">
+        <v>46283</v>
+      </c>
+      <c r="U24" s="14">
+        <v>46284</v>
+      </c>
+      <c r="V24" s="14">
+        <v>46285</v>
+      </c>
+      <c r="W24" s="13">
+        <v>46286</v>
+      </c>
+      <c r="X24" s="13">
+        <v>46287</v>
+      </c>
+      <c r="Y24" s="13">
+        <v>46288</v>
+      </c>
+      <c r="Z24" s="13">
+        <v>46289</v>
+      </c>
+      <c r="AA24" s="13">
+        <v>46290</v>
+      </c>
+      <c r="AB24" s="14">
+        <v>46291</v>
+      </c>
+      <c r="AC24" s="14">
+        <v>46292</v>
+      </c>
+      <c r="AD24" s="13">
+        <v>46293</v>
+      </c>
+      <c r="AE24" s="13">
+        <v>46294</v>
+      </c>
+      <c r="AF24" s="13">
+        <v>46295</v>
+      </c>
+      <c r="AG24" s="13"/>
+    </row>
+    <row r="25" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="B25" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="8">
+        <v>0</v>
+      </c>
+      <c r="D25" s="8">
+        <v>0</v>
+      </c>
+      <c r="E25" s="8">
+        <v>0</v>
+      </c>
+      <c r="F25" s="8">
+        <v>0</v>
+      </c>
+      <c r="G25" s="8"/>
+      <c r="H25" s="8"/>
+      <c r="I25" s="8">
+        <v>0</v>
+      </c>
+      <c r="J25" s="8">
+        <v>0</v>
+      </c>
+      <c r="K25" s="8">
+        <v>0</v>
+      </c>
+      <c r="L25" s="8">
+        <v>0</v>
+      </c>
+      <c r="M25" s="8">
+        <v>0</v>
+      </c>
+      <c r="N25" s="8"/>
+      <c r="O25" s="8"/>
+      <c r="P25" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="8">
+        <v>0</v>
+      </c>
+      <c r="R25" s="8">
+        <v>0</v>
+      </c>
+      <c r="S25" s="8">
+        <v>0</v>
+      </c>
+      <c r="T25" s="8">
+        <v>0</v>
+      </c>
+      <c r="U25" s="8"/>
+      <c r="V25" s="8"/>
+      <c r="W25" s="8">
+        <v>0</v>
+      </c>
+      <c r="X25" s="8">
+        <v>0</v>
+      </c>
+      <c r="Y25" s="8">
+        <v>0</v>
+      </c>
+      <c r="Z25" s="8">
+        <v>0</v>
+      </c>
+      <c r="AA25" s="8">
+        <v>0</v>
+      </c>
+      <c r="AB25" s="8"/>
+      <c r="AC25" s="8"/>
+      <c r="AD25" s="8">
+        <v>0</v>
+      </c>
+      <c r="AE25" s="8">
+        <v>0</v>
+      </c>
+      <c r="AF25" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="8">
+        <v>0</v>
+      </c>
+      <c r="D26" s="8">
+        <v>0</v>
+      </c>
+      <c r="E26" s="8">
+        <v>0</v>
+      </c>
+      <c r="F26" s="8">
+        <v>0</v>
+      </c>
+      <c r="G26" s="8"/>
+      <c r="H26" s="8"/>
+      <c r="I26" s="8">
+        <v>0</v>
+      </c>
+      <c r="J26" s="8">
+        <v>0</v>
+      </c>
+      <c r="K26" s="8">
+        <v>0</v>
+      </c>
+      <c r="L26" s="8">
+        <v>0</v>
+      </c>
+      <c r="M26" s="8">
+        <v>0</v>
+      </c>
+      <c r="N26" s="8"/>
+      <c r="O26" s="8"/>
+      <c r="P26" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="8">
+        <v>0</v>
+      </c>
+      <c r="R26" s="8">
+        <v>0</v>
+      </c>
+      <c r="S26" s="8">
+        <v>0</v>
+      </c>
+      <c r="T26" s="8">
+        <v>0</v>
+      </c>
+      <c r="U26" s="8"/>
+      <c r="V26" s="8"/>
+      <c r="W26" s="8">
+        <v>0</v>
+      </c>
+      <c r="X26" s="8">
+        <v>0</v>
+      </c>
+      <c r="Y26" s="8">
+        <v>0</v>
+      </c>
+      <c r="Z26" s="8">
+        <v>0</v>
+      </c>
+      <c r="AA26" s="8">
+        <v>0</v>
+      </c>
+      <c r="AB26" s="8"/>
+      <c r="AC26" s="8"/>
+      <c r="AD26" s="8">
+        <v>0</v>
+      </c>
+      <c r="AE26" s="8">
+        <v>0</v>
+      </c>
+      <c r="AF26" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="B27" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C27" s="8">
+        <v>0</v>
+      </c>
+      <c r="D27" s="8">
+        <v>0</v>
+      </c>
+      <c r="E27" s="8">
+        <v>0</v>
+      </c>
+      <c r="F27" s="8">
+        <v>0</v>
+      </c>
+      <c r="G27" s="8"/>
+      <c r="H27" s="8"/>
+      <c r="I27" s="8">
+        <v>0</v>
+      </c>
+      <c r="J27" s="8">
+        <v>0</v>
+      </c>
+      <c r="K27" s="8">
+        <v>0</v>
+      </c>
+      <c r="L27" s="8">
+        <v>0</v>
+      </c>
+      <c r="M27" s="8">
+        <v>0</v>
+      </c>
+      <c r="N27" s="8"/>
+      <c r="O27" s="8"/>
+      <c r="P27" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="8">
+        <v>0</v>
+      </c>
+      <c r="R27" s="8">
+        <v>0</v>
+      </c>
+      <c r="S27" s="8">
+        <v>0</v>
+      </c>
+      <c r="T27" s="8">
+        <v>0</v>
+      </c>
+      <c r="U27" s="8"/>
+      <c r="V27" s="8"/>
+      <c r="W27" s="8">
+        <v>0</v>
+      </c>
+      <c r="X27" s="8">
+        <v>0</v>
+      </c>
+      <c r="Y27" s="8">
+        <v>0</v>
+      </c>
+      <c r="Z27" s="8">
+        <v>0</v>
+      </c>
+      <c r="AA27" s="8">
+        <v>0</v>
+      </c>
+      <c r="AB27" s="8"/>
+      <c r="AC27" s="8"/>
+      <c r="AD27" s="8">
+        <v>0</v>
+      </c>
+      <c r="AE27" s="8">
+        <v>0</v>
+      </c>
+      <c r="AF27" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C28" s="8">
+        <v>0</v>
+      </c>
+      <c r="D28" s="8">
+        <v>0</v>
+      </c>
+      <c r="E28" s="8">
+        <v>0</v>
+      </c>
+      <c r="F28" s="8">
+        <v>0</v>
+      </c>
+      <c r="G28" s="8"/>
+      <c r="H28" s="8"/>
+      <c r="I28" s="8">
+        <v>0</v>
+      </c>
+      <c r="J28" s="8">
+        <v>0</v>
+      </c>
+      <c r="K28" s="8">
+        <v>0</v>
+      </c>
+      <c r="L28" s="8">
+        <v>0</v>
+      </c>
+      <c r="M28" s="8">
+        <v>0</v>
+      </c>
+      <c r="N28" s="8"/>
+      <c r="O28" s="8"/>
+      <c r="P28" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="8">
+        <v>0</v>
+      </c>
+      <c r="R28" s="8">
+        <v>0</v>
+      </c>
+      <c r="S28" s="8">
+        <v>0</v>
+      </c>
+      <c r="T28" s="8">
+        <v>0</v>
+      </c>
+      <c r="U28" s="8"/>
+      <c r="V28" s="8"/>
+      <c r="W28" s="8">
+        <v>0</v>
+      </c>
+      <c r="X28" s="8">
+        <v>0</v>
+      </c>
+      <c r="Y28" s="8">
+        <v>0</v>
+      </c>
+      <c r="Z28" s="8">
+        <v>0</v>
+      </c>
+      <c r="AA28" s="8">
+        <v>0</v>
+      </c>
+      <c r="AB28" s="8"/>
+      <c r="AC28" s="8"/>
+      <c r="AD28" s="8">
+        <v>0</v>
+      </c>
+      <c r="AE28" s="8">
+        <v>0</v>
+      </c>
+      <c r="AF28" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="B29" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C29" s="8">
+        <v>0</v>
+      </c>
+      <c r="D29" s="8">
+        <v>0</v>
+      </c>
+      <c r="E29" s="8">
+        <v>0</v>
+      </c>
+      <c r="F29" s="8">
+        <v>0</v>
+      </c>
+      <c r="G29" s="8"/>
+      <c r="H29" s="8"/>
+      <c r="I29" s="8">
+        <v>0</v>
+      </c>
+      <c r="J29" s="8">
+        <v>0</v>
+      </c>
+      <c r="K29" s="8">
+        <v>0</v>
+      </c>
+      <c r="L29" s="8">
+        <v>0</v>
+      </c>
+      <c r="M29" s="8">
+        <v>0</v>
+      </c>
+      <c r="N29" s="8"/>
+      <c r="O29" s="8"/>
+      <c r="P29" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="8">
+        <v>0</v>
+      </c>
+      <c r="R29" s="8">
+        <v>0</v>
+      </c>
+      <c r="S29" s="8">
+        <v>0</v>
+      </c>
+      <c r="T29" s="8">
+        <v>0</v>
+      </c>
+      <c r="U29" s="8"/>
+      <c r="V29" s="8"/>
+      <c r="W29" s="8">
+        <v>0</v>
+      </c>
+      <c r="X29" s="8">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="8">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="8">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="8">
+        <v>0</v>
+      </c>
+      <c r="AB29" s="8"/>
+      <c r="AC29" s="8"/>
+      <c r="AD29" s="8">
+        <v>0</v>
+      </c>
+      <c r="AE29" s="8">
+        <v>0</v>
+      </c>
+      <c r="AF29" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="B30" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C30" s="8">
+        <v>0</v>
+      </c>
+      <c r="D30" s="8">
+        <v>0</v>
+      </c>
+      <c r="E30" s="8">
+        <v>0</v>
+      </c>
+      <c r="F30" s="8">
+        <v>0</v>
+      </c>
+      <c r="G30" s="8"/>
+      <c r="H30" s="8"/>
+      <c r="I30" s="8">
+        <v>0</v>
+      </c>
+      <c r="J30" s="8">
+        <v>0</v>
+      </c>
+      <c r="K30" s="8">
+        <v>0</v>
+      </c>
+      <c r="L30" s="8">
+        <v>0</v>
+      </c>
+      <c r="M30" s="8">
+        <v>0</v>
+      </c>
+      <c r="N30" s="8"/>
+      <c r="O30" s="8"/>
+      <c r="P30" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="8">
+        <v>0</v>
+      </c>
+      <c r="R30" s="8">
+        <v>0</v>
+      </c>
+      <c r="S30" s="8">
+        <v>0</v>
+      </c>
+      <c r="T30" s="8">
+        <v>0</v>
+      </c>
+      <c r="U30" s="8"/>
+      <c r="V30" s="8"/>
+      <c r="W30" s="8">
+        <v>0</v>
+      </c>
+      <c r="X30" s="8">
+        <v>0</v>
+      </c>
+      <c r="Y30" s="8">
+        <v>0</v>
+      </c>
+      <c r="Z30" s="8">
+        <v>0</v>
+      </c>
+      <c r="AA30" s="8">
+        <v>0</v>
+      </c>
+      <c r="AB30" s="8"/>
+      <c r="AC30" s="8"/>
+      <c r="AD30" s="8">
+        <v>0</v>
+      </c>
+      <c r="AE30" s="8">
+        <v>0</v>
+      </c>
+      <c r="AF30" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="B31" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="C31" s="8">
+        <v>0</v>
+      </c>
+      <c r="D31" s="8">
+        <v>0</v>
+      </c>
+      <c r="E31" s="8">
+        <v>0</v>
+      </c>
+      <c r="F31" s="8">
+        <v>0</v>
+      </c>
+      <c r="G31" s="8"/>
+      <c r="H31" s="8"/>
+      <c r="I31" s="8">
+        <v>0</v>
+      </c>
+      <c r="J31" s="8">
+        <v>0</v>
+      </c>
+      <c r="K31" s="8">
+        <v>0</v>
+      </c>
+      <c r="L31" s="8">
+        <v>0</v>
+      </c>
+      <c r="M31" s="8">
+        <v>0</v>
+      </c>
+      <c r="N31" s="8"/>
+      <c r="O31" s="8"/>
+      <c r="P31" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="8">
+        <v>0</v>
+      </c>
+      <c r="R31" s="8">
+        <v>0</v>
+      </c>
+      <c r="S31" s="8">
+        <v>0</v>
+      </c>
+      <c r="T31" s="8">
+        <v>0</v>
+      </c>
+      <c r="U31" s="8"/>
+      <c r="V31" s="8"/>
+      <c r="W31" s="8">
+        <v>0</v>
+      </c>
+      <c r="X31" s="8">
+        <v>0</v>
+      </c>
+      <c r="Y31" s="8">
+        <v>0</v>
+      </c>
+      <c r="Z31" s="8">
+        <v>0</v>
+      </c>
+      <c r="AA31" s="8">
+        <v>0</v>
+      </c>
+      <c r="AB31" s="8"/>
+      <c r="AC31" s="8"/>
+      <c r="AD31" s="8">
+        <v>0</v>
+      </c>
+      <c r="AE31" s="8">
+        <v>0</v>
+      </c>
+      <c r="AF31" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="B32" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="C32" s="8">
+        <v>0</v>
+      </c>
+      <c r="D32" s="8">
+        <v>0</v>
+      </c>
+      <c r="E32" s="8">
+        <v>0</v>
+      </c>
+      <c r="F32" s="8">
+        <v>0</v>
+      </c>
+      <c r="G32" s="8"/>
+      <c r="H32" s="8"/>
+      <c r="I32" s="8">
+        <v>0</v>
+      </c>
+      <c r="J32" s="8">
+        <v>0</v>
+      </c>
+      <c r="K32" s="8">
+        <v>0</v>
+      </c>
+      <c r="L32" s="8">
+        <v>0</v>
+      </c>
+      <c r="M32" s="8">
+        <v>0</v>
+      </c>
+      <c r="N32" s="8"/>
+      <c r="O32" s="8"/>
+      <c r="P32" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="8">
+        <v>0</v>
+      </c>
+      <c r="R32" s="8">
+        <v>0</v>
+      </c>
+      <c r="S32" s="8">
+        <v>0</v>
+      </c>
+      <c r="T32" s="8">
+        <v>0</v>
+      </c>
+      <c r="U32" s="8"/>
+      <c r="V32" s="8"/>
+      <c r="W32" s="8">
+        <v>0</v>
+      </c>
+      <c r="X32" s="8">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="8">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="8">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="8">
+        <v>0</v>
+      </c>
+      <c r="AB32" s="8"/>
+      <c r="AC32" s="8"/>
+      <c r="AD32" s="8">
+        <v>0</v>
+      </c>
+      <c r="AE32" s="8">
+        <v>0</v>
+      </c>
+      <c r="AF32" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="B33" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C33" s="8">
+        <v>0</v>
+      </c>
+      <c r="D33" s="8">
+        <v>0</v>
+      </c>
+      <c r="E33" s="8">
+        <v>0</v>
+      </c>
+      <c r="F33" s="8">
+        <v>0</v>
+      </c>
+      <c r="G33" s="8"/>
+      <c r="H33" s="8"/>
+      <c r="I33" s="8">
+        <v>0</v>
+      </c>
+      <c r="J33" s="8">
+        <v>0</v>
+      </c>
+      <c r="K33" s="8">
+        <v>0</v>
+      </c>
+      <c r="L33" s="8">
+        <v>0</v>
+      </c>
+      <c r="M33" s="8">
+        <v>0</v>
+      </c>
+      <c r="N33" s="8"/>
+      <c r="O33" s="8"/>
+      <c r="P33" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="8">
+        <v>0</v>
+      </c>
+      <c r="R33" s="8">
+        <v>0</v>
+      </c>
+      <c r="S33" s="8">
+        <v>0</v>
+      </c>
+      <c r="T33" s="8">
+        <v>0</v>
+      </c>
+      <c r="U33" s="8"/>
+      <c r="V33" s="8"/>
+      <c r="W33" s="8">
+        <v>0</v>
+      </c>
+      <c r="X33" s="8">
+        <v>0</v>
+      </c>
+      <c r="Y33" s="8">
+        <v>0</v>
+      </c>
+      <c r="Z33" s="8">
+        <v>0</v>
+      </c>
+      <c r="AA33" s="8">
+        <v>0</v>
+      </c>
+      <c r="AB33" s="8"/>
+      <c r="AC33" s="8"/>
+      <c r="AD33" s="8">
+        <v>0</v>
+      </c>
+      <c r="AE33" s="8">
+        <v>0</v>
+      </c>
+      <c r="AF33" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="B34" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="C34" s="8">
+        <v>0</v>
+      </c>
+      <c r="D34" s="8">
+        <v>0</v>
+      </c>
+      <c r="E34" s="8">
+        <v>0</v>
+      </c>
+      <c r="F34" s="8">
+        <v>0</v>
+      </c>
+      <c r="G34" s="8"/>
+      <c r="H34" s="8"/>
+      <c r="I34" s="8">
+        <v>0</v>
+      </c>
+      <c r="J34" s="8">
+        <v>0</v>
+      </c>
+      <c r="K34" s="8">
+        <v>0</v>
+      </c>
+      <c r="L34" s="8">
+        <v>0</v>
+      </c>
+      <c r="M34" s="8">
+        <v>0</v>
+      </c>
+      <c r="N34" s="8"/>
+      <c r="O34" s="8"/>
+      <c r="P34" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="8">
+        <v>0</v>
+      </c>
+      <c r="R34" s="8">
+        <v>0</v>
+      </c>
+      <c r="S34" s="8">
+        <v>0</v>
+      </c>
+      <c r="T34" s="8">
+        <v>0</v>
+      </c>
+      <c r="U34" s="8"/>
+      <c r="V34" s="8"/>
+      <c r="W34" s="8">
+        <v>0</v>
+      </c>
+      <c r="X34" s="8">
+        <v>0</v>
+      </c>
+      <c r="Y34" s="8">
+        <v>0</v>
+      </c>
+      <c r="Z34" s="8">
+        <v>0</v>
+      </c>
+      <c r="AA34" s="8">
+        <v>0</v>
+      </c>
+      <c r="AB34" s="8"/>
+      <c r="AC34" s="8"/>
+      <c r="AD34" s="8">
+        <v>0</v>
+      </c>
+      <c r="AE34" s="8">
+        <v>0</v>
+      </c>
+      <c r="AF34" s="8">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:A23" xr:uid="{00000000-0001-0000-0200-000000000000}"/>
+  <autoFilter ref="A1:A34" xr:uid="{00000000-0001-0000-0200-000000000000}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="Agosto"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/dados.xlsx
+++ b/dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://concresupersc-my.sharepoint.com/personal/marketing_concresupersc_onmicrosoft_com/Documents/Área de Trabalho/C.I.V/Dashbord/DASHBOARD-METAS-PROPOSTAS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="619" documentId="8_{A291900F-2FC4-4CBC-95EF-8FF0E06A2678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3D3DAB29-07B1-4FF3-8CC3-C814EFC254B2}"/>
+  <xr:revisionPtr revIDLastSave="639" documentId="8_{A291900F-2FC4-4CBC-95EF-8FF0E06A2678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{57D7DF53-EA23-406C-86C0-7ED18BCE4922}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="34785" yWindow="-3135" windowWidth="14610" windowHeight="15585" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dados Diários" sheetId="1" r:id="rId1"/>
@@ -10523,7 +10523,9 @@
       <c r="C465" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D465" s="2"/>
+      <c r="D465" s="2">
+        <v>3046.5</v>
+      </c>
       <c r="E465" s="3">
         <v>4477.5</v>
       </c>
@@ -10542,7 +10544,9 @@
       <c r="C466" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D466" s="2"/>
+      <c r="D466" s="2">
+        <v>3102.5</v>
+      </c>
       <c r="E466" s="3">
         <v>3980</v>
       </c>
@@ -10561,7 +10565,9 @@
       <c r="C467" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D467" s="2"/>
+      <c r="D467" s="2">
+        <v>904</v>
+      </c>
       <c r="E467" s="3">
         <v>1492.5</v>
       </c>
@@ -10580,7 +10586,9 @@
       <c r="C468" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D468" s="2"/>
+      <c r="D468" s="2">
+        <v>2787</v>
+      </c>
       <c r="E468" s="3">
         <v>4170</v>
       </c>
@@ -10599,7 +10607,9 @@
       <c r="C469" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D469" s="2"/>
+      <c r="D469" s="2">
+        <v>2203.5</v>
+      </c>
       <c r="E469" s="3">
         <v>2780</v>
       </c>
@@ -10618,7 +10628,9 @@
       <c r="C470" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D470" s="2"/>
+      <c r="D470" s="2">
+        <v>1725.5</v>
+      </c>
       <c r="E470" s="3">
         <v>1710</v>
       </c>
@@ -10637,7 +10649,9 @@
       <c r="C471" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D471" s="2"/>
+      <c r="D471" s="2">
+        <v>2442.5</v>
+      </c>
       <c r="E471" s="3">
         <v>1610</v>
       </c>
@@ -10656,7 +10670,9 @@
       <c r="C472" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D472" s="2"/>
+      <c r="D472" s="2">
+        <v>656</v>
+      </c>
       <c r="E472" s="3">
         <v>1120</v>
       </c>
@@ -10675,7 +10691,9 @@
       <c r="C473" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D473" s="2"/>
+      <c r="D473" s="2">
+        <v>1302.5</v>
+      </c>
       <c r="E473" s="3">
         <v>1405</v>
       </c>
@@ -10694,7 +10712,9 @@
       <c r="C474" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="D474" s="2"/>
+      <c r="D474" s="2">
+        <v>790.5</v>
+      </c>
       <c r="E474" s="3">
         <v>1000</v>
       </c>
@@ -17468,7 +17488,7 @@
         <v>6</v>
       </c>
       <c r="AC14" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD14" s="8">
         <v>0</v>
@@ -17549,7 +17569,7 @@
         <v>4</v>
       </c>
       <c r="AC15" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD15" s="8">
         <v>0</v>
@@ -17630,7 +17650,7 @@
         <v>3</v>
       </c>
       <c r="AC16" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD16" s="8">
         <v>0</v>
@@ -17711,7 +17731,7 @@
         <v>3</v>
       </c>
       <c r="AC17" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD17" s="8">
         <v>0</v>
@@ -17792,7 +17812,7 @@
         <v>0</v>
       </c>
       <c r="AC18" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD18" s="8">
         <v>0</v>
@@ -17954,7 +17974,7 @@
         <v>2</v>
       </c>
       <c r="AC20" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD20" s="8">
         <v>0</v>
@@ -18116,7 +18136,7 @@
         <v>1</v>
       </c>
       <c r="AC22" s="8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD22" s="8">
         <v>0</v>
@@ -18197,7 +18217,7 @@
         <v>1</v>
       </c>
       <c r="AC23" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD23" s="8">
         <v>0</v>

--- a/dados.xlsx
+++ b/dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://concresupersc-my.sharepoint.com/personal/marketing_concresupersc_onmicrosoft_com/Documents/Área de Trabalho/C.I.V/Dashbord/DASHBOARD-METAS-PROPOSTAS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="639" documentId="8_{A291900F-2FC4-4CBC-95EF-8FF0E06A2678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{57D7DF53-EA23-406C-86C0-7ED18BCE4922}"/>
+  <xr:revisionPtr revIDLastSave="676" documentId="8_{A291900F-2FC4-4CBC-95EF-8FF0E06A2678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B1FD45E5-DD94-4265-B166-97B06EF40AA1}"/>
   <bookViews>
-    <workbookView xWindow="34785" yWindow="-3135" windowWidth="14610" windowHeight="15585" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-3255" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dados Diários" sheetId="1" r:id="rId1"/>
@@ -369,7 +369,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -421,6 +421,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -735,7 +738,7 @@
     <col min="2" max="2" width="15.7109375" style="6" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="13.42578125" style="6" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.7109375" style="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.28515625" style="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18" style="6" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9.140625" style="6"/>
     <col min="8" max="8" width="25.7109375" style="6" customWidth="1"/>
     <col min="9" max="9" width="9.140625" style="6"/>
@@ -5885,7 +5888,7 @@
       <c r="C245" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D245" s="2">
+      <c r="D245" s="19">
         <v>41.5</v>
       </c>
       <c r="E245" s="3">
@@ -5907,7 +5910,7 @@
       <c r="C246" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D246" s="2">
+      <c r="D246" s="19">
         <v>62</v>
       </c>
       <c r="E246" s="3">
@@ -5929,7 +5932,7 @@
       <c r="C247" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D247" s="2">
+      <c r="D247" s="19">
         <v>9</v>
       </c>
       <c r="E247" s="3">
@@ -5951,7 +5954,7 @@
       <c r="C248" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D248" s="2">
+      <c r="D248" s="19">
         <v>64</v>
       </c>
       <c r="E248" s="3">
@@ -5973,7 +5976,7 @@
       <c r="C249" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D249" s="2">
+      <c r="D249" s="19">
         <v>42</v>
       </c>
       <c r="E249" s="3">
@@ -5995,7 +5998,7 @@
       <c r="C250" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D250" s="2">
+      <c r="D250" s="19">
         <v>38.5</v>
       </c>
       <c r="E250" s="3">
@@ -6017,7 +6020,7 @@
       <c r="C251" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D251" s="2">
+      <c r="D251" s="19">
         <v>46</v>
       </c>
       <c r="E251" s="3">
@@ -6039,7 +6042,7 @@
       <c r="C252" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D252" s="2">
+      <c r="D252" s="19">
         <v>0</v>
       </c>
       <c r="E252" s="3">
@@ -6061,7 +6064,7 @@
       <c r="C253" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D253" s="2">
+      <c r="D253" s="19">
         <v>0</v>
       </c>
       <c r="E253" s="3">
@@ -6083,7 +6086,7 @@
       <c r="C254" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="D254" s="2">
+      <c r="D254" s="19">
         <v>24</v>
       </c>
       <c r="E254" s="3">
@@ -6103,7 +6106,7 @@
       <c r="C255" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D255" s="2">
+      <c r="D255" s="19">
         <v>291</v>
       </c>
       <c r="E255" s="3">
@@ -6125,7 +6128,7 @@
       <c r="C256" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D256" s="2">
+      <c r="D256" s="19">
         <v>256</v>
       </c>
       <c r="E256" s="3">
@@ -6147,7 +6150,7 @@
       <c r="C257" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D257" s="2">
+      <c r="D257" s="19">
         <v>18</v>
       </c>
       <c r="E257" s="3">
@@ -6169,7 +6172,7 @@
       <c r="C258" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D258" s="2">
+      <c r="D258" s="19">
         <v>238.5</v>
       </c>
       <c r="E258" s="3">
@@ -6191,7 +6194,7 @@
       <c r="C259" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D259" s="2">
+      <c r="D259" s="19">
         <v>102</v>
       </c>
       <c r="E259" s="3">
@@ -6213,7 +6216,7 @@
       <c r="C260" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D260" s="2">
+      <c r="D260" s="19">
         <v>138.5</v>
       </c>
       <c r="E260" s="3">
@@ -6235,7 +6238,7 @@
       <c r="C261" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D261" s="2">
+      <c r="D261" s="19">
         <v>213.5</v>
       </c>
       <c r="E261" s="3">
@@ -6257,7 +6260,7 @@
       <c r="C262" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D262" s="2">
+      <c r="D262" s="19">
         <v>25.5</v>
       </c>
       <c r="E262" s="3">
@@ -6279,7 +6282,7 @@
       <c r="C263" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D263" s="2">
+      <c r="D263" s="19">
         <v>58.5</v>
       </c>
       <c r="E263" s="3">
@@ -6301,7 +6304,7 @@
       <c r="C264" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="D264" s="2">
+      <c r="D264" s="19">
         <v>96</v>
       </c>
       <c r="E264" s="3">
@@ -6323,7 +6326,7 @@
       <c r="C265" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D265" s="2">
+      <c r="D265" s="19">
         <v>538</v>
       </c>
       <c r="E265" s="3">
@@ -6344,7 +6347,7 @@
       <c r="C266" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D266" s="2">
+      <c r="D266" s="19">
         <v>332.5</v>
       </c>
       <c r="E266" s="3">
@@ -6365,7 +6368,7 @@
       <c r="C267" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D267" s="2">
+      <c r="D267" s="19">
         <v>30.5</v>
       </c>
       <c r="E267" s="3">
@@ -6386,7 +6389,7 @@
       <c r="C268" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D268" s="2">
+      <c r="D268" s="19">
         <v>466</v>
       </c>
       <c r="E268" s="3">
@@ -6407,7 +6410,7 @@
       <c r="C269" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D269" s="2">
+      <c r="D269" s="19">
         <v>189</v>
       </c>
       <c r="E269" s="3">
@@ -6428,7 +6431,7 @@
       <c r="C270" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D270" s="2">
+      <c r="D270" s="19">
         <v>228.5</v>
       </c>
       <c r="E270" s="3">
@@ -6449,7 +6452,7 @@
       <c r="C271" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D271" s="2">
+      <c r="D271" s="19">
         <v>305.5</v>
       </c>
       <c r="E271" s="3">
@@ -6470,7 +6473,7 @@
       <c r="C272" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D272" s="2">
+      <c r="D272" s="19">
         <v>68.5</v>
       </c>
       <c r="E272" s="3">
@@ -6491,7 +6494,7 @@
       <c r="C273" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D273" s="2">
+      <c r="D273" s="19">
         <v>127</v>
       </c>
       <c r="E273" s="3">
@@ -6512,7 +6515,7 @@
       <c r="C274" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="D274" s="2">
+      <c r="D274" s="19">
         <v>152</v>
       </c>
       <c r="E274" s="3">
@@ -6533,7 +6536,7 @@
       <c r="C275" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D275" s="2">
+      <c r="D275" s="19">
         <v>283</v>
       </c>
       <c r="E275" s="3">
@@ -6554,7 +6557,7 @@
       <c r="C276" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D276" s="2">
+      <c r="D276" s="19">
         <v>373</v>
       </c>
       <c r="E276" s="3">
@@ -6575,7 +6578,7 @@
       <c r="C277" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D277" s="2">
+      <c r="D277" s="19">
         <v>119</v>
       </c>
       <c r="E277" s="3">
@@ -6596,7 +6599,7 @@
       <c r="C278" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D278" s="2">
+      <c r="D278" s="19">
         <v>621.5</v>
       </c>
       <c r="E278" s="3">
@@ -6617,7 +6620,7 @@
       <c r="C279" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D279" s="2">
+      <c r="D279" s="19">
         <v>278</v>
       </c>
       <c r="E279" s="3">
@@ -6638,7 +6641,7 @@
       <c r="C280" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D280" s="2">
+      <c r="D280" s="19">
         <v>280.5</v>
       </c>
       <c r="E280" s="3">
@@ -6659,7 +6662,7 @@
       <c r="C281" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D281" s="2">
+      <c r="D281" s="19">
         <v>390.5</v>
       </c>
       <c r="E281" s="3">
@@ -6680,7 +6683,7 @@
       <c r="C282" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D282" s="2">
+      <c r="D282" s="19">
         <v>155</v>
       </c>
       <c r="E282" s="3">
@@ -6701,7 +6704,7 @@
       <c r="C283" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D283" s="2">
+      <c r="D283" s="19">
         <v>159</v>
       </c>
       <c r="E283" s="3">
@@ -6722,7 +6725,7 @@
       <c r="C284" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="D284" s="2">
+      <c r="D284" s="19">
         <v>184</v>
       </c>
       <c r="E284" s="3">
@@ -6743,7 +6746,7 @@
       <c r="C285" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D285" s="2">
+      <c r="D285" s="19">
         <v>490.5</v>
       </c>
       <c r="E285" s="3">
@@ -6764,7 +6767,7 @@
       <c r="C286" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D286" s="2">
+      <c r="D286" s="19">
         <v>593</v>
       </c>
       <c r="E286" s="3">
@@ -6785,7 +6788,7 @@
       <c r="C287" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D287" s="2">
+      <c r="D287" s="19">
         <v>123</v>
       </c>
       <c r="E287" s="3">
@@ -6806,7 +6809,7 @@
       <c r="C288" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D288" s="2">
+      <c r="D288" s="19">
         <v>720.5</v>
       </c>
       <c r="E288" s="3">
@@ -6827,7 +6830,7 @@
       <c r="C289" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D289" s="2">
+      <c r="D289" s="19">
         <v>352.5</v>
       </c>
       <c r="E289" s="3">
@@ -6848,7 +6851,7 @@
       <c r="C290" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D290" s="2">
+      <c r="D290" s="19">
         <v>398</v>
       </c>
       <c r="E290" s="3">
@@ -6869,7 +6872,7 @@
       <c r="C291" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D291" s="2">
+      <c r="D291" s="19">
         <v>446</v>
       </c>
       <c r="E291" s="3">
@@ -6890,7 +6893,7 @@
       <c r="C292" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D292" s="2">
+      <c r="D292" s="19">
         <v>160</v>
       </c>
       <c r="E292" s="3">
@@ -6911,7 +6914,7 @@
       <c r="C293" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D293" s="2">
+      <c r="D293" s="19">
         <v>166</v>
       </c>
       <c r="E293" s="3">
@@ -6932,7 +6935,7 @@
       <c r="C294" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="D294" s="2">
+      <c r="D294" s="19">
         <v>219</v>
       </c>
       <c r="E294" s="3">
@@ -6953,7 +6956,7 @@
       <c r="C295" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D295" s="2">
+      <c r="D295" s="19">
         <v>648.5</v>
       </c>
       <c r="E295" s="3">
@@ -6974,7 +6977,7 @@
       <c r="C296" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D296" s="2">
+      <c r="D296" s="19">
         <v>693.5</v>
       </c>
       <c r="E296" s="3">
@@ -6995,7 +6998,7 @@
       <c r="C297" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D297" s="2">
+      <c r="D297" s="19">
         <v>152</v>
       </c>
       <c r="E297" s="3">
@@ -7016,7 +7019,7 @@
       <c r="C298" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D298" s="2">
+      <c r="D298" s="19">
         <v>742</v>
       </c>
       <c r="E298" s="3">
@@ -7037,7 +7040,7 @@
       <c r="C299" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D299" s="2">
+      <c r="D299" s="19">
         <v>447</v>
       </c>
       <c r="E299" s="3">
@@ -7058,7 +7061,7 @@
       <c r="C300" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D300" s="2">
+      <c r="D300" s="19">
         <v>432</v>
       </c>
       <c r="E300" s="3">
@@ -7079,7 +7082,7 @@
       <c r="C301" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D301" s="2">
+      <c r="D301" s="19">
         <v>490.5</v>
       </c>
       <c r="E301" s="3">
@@ -7100,7 +7103,7 @@
       <c r="C302" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D302" s="2">
+      <c r="D302" s="19">
         <v>160</v>
       </c>
       <c r="E302" s="3">
@@ -7121,7 +7124,7 @@
       <c r="C303" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D303" s="2">
+      <c r="D303" s="19">
         <v>173</v>
       </c>
       <c r="E303" s="3">
@@ -7142,7 +7145,7 @@
       <c r="C304" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="D304" s="2">
+      <c r="D304" s="19">
         <v>224.5</v>
       </c>
       <c r="E304" s="3">
@@ -7163,7 +7166,7 @@
       <c r="C305" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D305" s="2">
+      <c r="D305" s="19">
         <v>694.5</v>
       </c>
       <c r="E305" s="3">
@@ -7184,7 +7187,7 @@
       <c r="C306" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D306" s="2">
+      <c r="D306" s="19">
         <v>693.5</v>
       </c>
       <c r="E306" s="3">
@@ -7205,7 +7208,7 @@
       <c r="C307" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D307" s="2">
+      <c r="D307" s="19">
         <v>152</v>
       </c>
       <c r="E307" s="3">
@@ -7226,7 +7229,7 @@
       <c r="C308" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D308" s="2">
+      <c r="D308" s="19">
         <v>798.5</v>
       </c>
       <c r="E308" s="3">
@@ -7247,7 +7250,7 @@
       <c r="C309" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D309" s="2">
+      <c r="D309" s="19">
         <v>492</v>
       </c>
       <c r="E309" s="3">
@@ -7268,7 +7271,7 @@
       <c r="C310" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D310" s="2">
+      <c r="D310" s="19">
         <v>446</v>
       </c>
       <c r="E310" s="3">
@@ -7289,7 +7292,7 @@
       <c r="C311" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D311" s="2">
+      <c r="D311" s="19">
         <v>490.5</v>
       </c>
       <c r="E311" s="3">
@@ -7310,7 +7313,7 @@
       <c r="C312" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D312" s="2">
+      <c r="D312" s="19">
         <v>160</v>
       </c>
       <c r="E312" s="3">
@@ -7331,7 +7334,7 @@
       <c r="C313" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D313" s="2">
+      <c r="D313" s="19">
         <v>173</v>
       </c>
       <c r="E313" s="3">
@@ -7352,7 +7355,7 @@
       <c r="C314" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="D314" s="2">
+      <c r="D314" s="19">
         <v>224.5</v>
       </c>
       <c r="E314" s="3">
@@ -7373,7 +7376,7 @@
       <c r="C315" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D315" s="2">
+      <c r="D315" s="19">
         <v>778.5</v>
       </c>
       <c r="E315" s="3">
@@ -7394,7 +7397,7 @@
       <c r="C316" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D316" s="2">
+      <c r="D316" s="19">
         <v>801</v>
       </c>
       <c r="E316" s="3">
@@ -7415,7 +7418,7 @@
       <c r="C317" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D317" s="2">
+      <c r="D317" s="19">
         <v>214.5</v>
       </c>
       <c r="E317" s="3">
@@ -7436,7 +7439,7 @@
       <c r="C318" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D318" s="2">
+      <c r="D318" s="19">
         <v>946</v>
       </c>
       <c r="E318" s="3">
@@ -7457,7 +7460,7 @@
       <c r="C319" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D319" s="2">
+      <c r="D319" s="19">
         <v>568</v>
       </c>
       <c r="E319" s="3">
@@ -7478,7 +7481,7 @@
       <c r="C320" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D320" s="2">
+      <c r="D320" s="19">
         <v>515</v>
       </c>
       <c r="E320" s="3">
@@ -7499,7 +7502,7 @@
       <c r="C321" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D321" s="2">
+      <c r="D321" s="19">
         <v>538.5</v>
       </c>
       <c r="E321" s="3">
@@ -7520,7 +7523,7 @@
       <c r="C322" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D322" s="2">
+      <c r="D322" s="19">
         <v>163</v>
       </c>
       <c r="E322" s="3">
@@ -7541,7 +7544,7 @@
       <c r="C323" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D323" s="2">
+      <c r="D323" s="19">
         <v>209</v>
       </c>
       <c r="E323" s="3">
@@ -7562,7 +7565,7 @@
       <c r="C324" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="D324" s="2">
+      <c r="D324" s="19">
         <v>229.5</v>
       </c>
       <c r="E324" s="3">
@@ -7583,7 +7586,7 @@
       <c r="C325" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D325" s="2">
+      <c r="D325" s="19">
         <v>1015.5</v>
       </c>
       <c r="E325" s="3">
@@ -7604,7 +7607,7 @@
       <c r="C326" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D326" s="2">
+      <c r="D326" s="19">
         <v>870</v>
       </c>
       <c r="E326" s="3">
@@ -7625,7 +7628,7 @@
       <c r="C327" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D327" s="2">
+      <c r="D327" s="19">
         <v>278</v>
       </c>
       <c r="E327" s="3">
@@ -7646,7 +7649,7 @@
       <c r="C328" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D328" s="2">
+      <c r="D328" s="19">
         <v>1089.5</v>
       </c>
       <c r="E328" s="3">
@@ -7667,7 +7670,7 @@
       <c r="C329" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D329" s="2">
+      <c r="D329" s="19">
         <v>698</v>
       </c>
       <c r="E329" s="3">
@@ -7688,7 +7691,7 @@
       <c r="C330" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D330" s="2">
+      <c r="D330" s="19">
         <v>605</v>
       </c>
       <c r="E330" s="3">
@@ -7709,7 +7712,7 @@
       <c r="C331" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D331" s="2">
+      <c r="D331" s="19">
         <v>668.5</v>
       </c>
       <c r="E331" s="3">
@@ -7730,7 +7733,7 @@
       <c r="C332" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D332" s="2">
+      <c r="D332" s="19">
         <v>208.5</v>
       </c>
       <c r="E332" s="3">
@@ -7751,7 +7754,7 @@
       <c r="C333" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D333" s="2">
+      <c r="D333" s="19">
         <v>278</v>
       </c>
       <c r="E333" s="3">
@@ -7772,7 +7775,7 @@
       <c r="C334" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="D334" s="2">
+      <c r="D334" s="19">
         <v>249.5</v>
       </c>
       <c r="E334" s="3">
@@ -7793,7 +7796,7 @@
       <c r="C335" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D335" s="2">
+      <c r="D335" s="19">
         <v>1225.5</v>
       </c>
       <c r="E335" s="3">
@@ -7814,7 +7817,7 @@
       <c r="C336" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D336" s="2">
+      <c r="D336" s="19">
         <v>1186</v>
       </c>
       <c r="E336" s="3">
@@ -7835,7 +7838,7 @@
       <c r="C337" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D337" s="2">
+      <c r="D337" s="19">
         <v>313.5</v>
       </c>
       <c r="E337" s="3">
@@ -7856,7 +7859,7 @@
       <c r="C338" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D338" s="2">
+      <c r="D338" s="19">
         <v>1244</v>
       </c>
       <c r="E338" s="3">
@@ -7877,7 +7880,7 @@
       <c r="C339" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D339" s="2">
+      <c r="D339" s="19">
         <v>804.5</v>
       </c>
       <c r="E339" s="3">
@@ -7898,7 +7901,7 @@
       <c r="C340" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D340" s="2">
+      <c r="D340" s="19">
         <v>628</v>
       </c>
       <c r="E340" s="3">
@@ -7919,7 +7922,7 @@
       <c r="C341" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D341" s="2">
+      <c r="D341" s="19">
         <v>809.5</v>
       </c>
       <c r="E341" s="3">
@@ -7940,7 +7943,7 @@
       <c r="C342" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D342" s="2">
+      <c r="D342" s="19">
         <v>233.5</v>
       </c>
       <c r="E342" s="3">
@@ -7961,7 +7964,7 @@
       <c r="C343" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D343" s="2">
+      <c r="D343" s="19">
         <v>336.5</v>
       </c>
       <c r="E343" s="3">
@@ -7982,7 +7985,7 @@
       <c r="C344" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="D344" s="2">
+      <c r="D344" s="19">
         <v>285</v>
       </c>
       <c r="E344" s="3">
@@ -8003,7 +8006,7 @@
       <c r="C345" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D345" s="2">
+      <c r="D345" s="19">
         <v>1368</v>
       </c>
       <c r="E345" s="3">
@@ -8024,7 +8027,7 @@
       <c r="C346" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D346" s="2">
+      <c r="D346" s="19">
         <v>1441.5</v>
       </c>
       <c r="E346" s="3">
@@ -8045,7 +8048,7 @@
       <c r="C347" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D347" s="2">
+      <c r="D347" s="19">
         <v>339</v>
       </c>
       <c r="E347" s="3">
@@ -8066,7 +8069,7 @@
       <c r="C348" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D348" s="2">
+      <c r="D348" s="19">
         <v>1442.5</v>
       </c>
       <c r="E348" s="3">
@@ -8087,7 +8090,7 @@
       <c r="C349" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D349" s="2">
+      <c r="D349" s="19">
         <v>887.5</v>
       </c>
       <c r="E349" s="3">
@@ -8108,7 +8111,7 @@
       <c r="C350" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D350" s="2">
+      <c r="D350" s="19">
         <v>696</v>
       </c>
       <c r="E350" s="3">
@@ -8129,7 +8132,7 @@
       <c r="C351" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D351" s="2">
+      <c r="D351" s="19">
         <v>966.5</v>
       </c>
       <c r="E351" s="3">
@@ -8150,7 +8153,7 @@
       <c r="C352" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D352" s="2">
+      <c r="D352" s="19">
         <v>236.5</v>
       </c>
       <c r="E352" s="3">
@@ -8171,7 +8174,7 @@
       <c r="C353" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D353" s="2">
+      <c r="D353" s="19">
         <v>394</v>
       </c>
       <c r="E353" s="3">
@@ -8192,7 +8195,7 @@
       <c r="C354" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="D354" s="2">
+      <c r="D354" s="19">
         <v>329.5</v>
       </c>
       <c r="E354" s="3">
@@ -8213,7 +8216,7 @@
       <c r="C355" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D355" s="2">
+      <c r="D355" s="19">
         <v>1552</v>
       </c>
       <c r="E355" s="3">
@@ -8234,7 +8237,7 @@
       <c r="C356" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D356" s="2">
+      <c r="D356" s="19">
         <v>1553</v>
       </c>
       <c r="E356" s="3">
@@ -8255,7 +8258,7 @@
       <c r="C357" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D357" s="2">
+      <c r="D357" s="19">
         <v>375</v>
       </c>
       <c r="E357" s="3">
@@ -8276,7 +8279,7 @@
       <c r="C358" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D358" s="2">
+      <c r="D358" s="19">
         <v>1533.5</v>
       </c>
       <c r="E358" s="3">
@@ -8297,7 +8300,7 @@
       <c r="C359" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D359" s="2">
+      <c r="D359" s="19">
         <v>978</v>
       </c>
       <c r="E359" s="3">
@@ -8318,7 +8321,7 @@
       <c r="C360" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D360" s="2">
+      <c r="D360" s="19">
         <v>774</v>
       </c>
       <c r="E360" s="3">
@@ -8339,7 +8342,7 @@
       <c r="C361" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D361" s="2">
+      <c r="D361" s="19">
         <v>1148.5</v>
       </c>
       <c r="E361" s="3">
@@ -8360,7 +8363,7 @@
       <c r="C362" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D362" s="2">
+      <c r="D362" s="19">
         <v>251.5</v>
       </c>
       <c r="E362" s="3">
@@ -8381,7 +8384,7 @@
       <c r="C363" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D363" s="2">
+      <c r="D363" s="19">
         <v>475.5</v>
       </c>
       <c r="E363" s="3">
@@ -8402,7 +8405,7 @@
       <c r="C364" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="D364" s="2">
+      <c r="D364" s="19">
         <v>405</v>
       </c>
       <c r="E364" s="3">
@@ -8423,7 +8426,7 @@
       <c r="C365" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D365" s="2">
+      <c r="D365" s="19">
         <v>1626.5</v>
       </c>
       <c r="E365" s="3">
@@ -8444,7 +8447,7 @@
       <c r="C366" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D366" s="2">
+      <c r="D366" s="19">
         <v>1630.5</v>
       </c>
       <c r="E366" s="3">
@@ -8465,7 +8468,7 @@
       <c r="C367" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D367" s="2">
+      <c r="D367" s="19">
         <v>383</v>
       </c>
       <c r="E367" s="3">
@@ -8486,7 +8489,7 @@
       <c r="C368" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D368" s="2">
+      <c r="D368" s="19">
         <v>1588.5</v>
       </c>
       <c r="E368" s="3">
@@ -8507,7 +8510,7 @@
       <c r="C369" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D369" s="2">
+      <c r="D369" s="19">
         <v>1044.5</v>
       </c>
       <c r="E369" s="3">
@@ -8528,7 +8531,7 @@
       <c r="C370" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D370" s="2">
+      <c r="D370" s="19">
         <v>792</v>
       </c>
       <c r="E370" s="3">
@@ -8549,7 +8552,7 @@
       <c r="C371" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D371" s="2">
+      <c r="D371" s="19">
         <v>1223</v>
       </c>
       <c r="E371" s="3">
@@ -8570,7 +8573,7 @@
       <c r="C372" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D372" s="2">
+      <c r="D372" s="19">
         <v>251.5</v>
       </c>
       <c r="E372" s="3">
@@ -8591,7 +8594,7 @@
       <c r="C373" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D373" s="2">
+      <c r="D373" s="19">
         <v>488.5</v>
       </c>
       <c r="E373" s="3">
@@ -8612,7 +8615,7 @@
       <c r="C374" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="D374" s="2">
+      <c r="D374" s="19">
         <v>427</v>
       </c>
       <c r="E374" s="3">
@@ -8633,7 +8636,7 @@
       <c r="C375" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D375" s="2">
+      <c r="D375" s="19">
         <v>1920</v>
       </c>
       <c r="E375" s="3">
@@ -8654,7 +8657,7 @@
       <c r="C376" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D376" s="2">
+      <c r="D376" s="19">
         <v>1920</v>
       </c>
       <c r="E376" s="3">
@@ -8675,7 +8678,7 @@
       <c r="C377" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D377" s="2">
+      <c r="D377" s="19">
         <v>396.5</v>
       </c>
       <c r="E377" s="3">
@@ -8696,7 +8699,7 @@
       <c r="C378" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D378" s="2">
+      <c r="D378" s="19">
         <v>1476</v>
       </c>
       <c r="E378" s="3">
@@ -8717,7 +8720,7 @@
       <c r="C379" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D379" s="2">
+      <c r="D379" s="19">
         <v>1118</v>
       </c>
       <c r="E379" s="3">
@@ -8738,7 +8741,7 @@
       <c r="C380" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D380" s="2">
+      <c r="D380" s="19">
         <v>846.5</v>
       </c>
       <c r="E380" s="3">
@@ -8759,7 +8762,7 @@
       <c r="C381" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D381" s="2">
+      <c r="D381" s="19">
         <v>1395.5</v>
       </c>
       <c r="E381" s="3">
@@ -8780,7 +8783,7 @@
       <c r="C382" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D382" s="2">
+      <c r="D382" s="19">
         <v>269</v>
       </c>
       <c r="E382" s="3">
@@ -8801,7 +8804,7 @@
       <c r="C383" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D383" s="2">
+      <c r="D383" s="19">
         <v>542</v>
       </c>
       <c r="E383" s="3">
@@ -8822,7 +8825,7 @@
       <c r="C384" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="D384" s="2">
+      <c r="D384" s="19">
         <v>456.5</v>
       </c>
       <c r="E384" s="3">
@@ -8843,7 +8846,7 @@
       <c r="C385" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D385" s="2">
+      <c r="D385" s="19">
         <v>2023.5</v>
       </c>
       <c r="E385" s="3">
@@ -8864,7 +8867,7 @@
       <c r="C386" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D386" s="2">
+      <c r="D386" s="19">
         <v>2211.5</v>
       </c>
       <c r="E386" s="3">
@@ -8885,7 +8888,7 @@
       <c r="C387" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D387" s="2">
+      <c r="D387" s="19">
         <v>494</v>
       </c>
       <c r="E387" s="3">
@@ -8906,7 +8909,7 @@
       <c r="C388" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D388" s="2">
+      <c r="D388" s="19">
         <v>1920</v>
       </c>
       <c r="E388" s="3">
@@ -8927,7 +8930,7 @@
       <c r="C389" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D389" s="2">
+      <c r="D389" s="19">
         <v>1188</v>
       </c>
       <c r="E389" s="3">
@@ -8948,7 +8951,7 @@
       <c r="C390" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D390" s="2">
+      <c r="D390" s="19">
         <v>957.5</v>
       </c>
       <c r="E390" s="3">
@@ -8969,7 +8972,7 @@
       <c r="C391" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D391" s="2">
+      <c r="D391" s="19">
         <v>1509.5</v>
       </c>
       <c r="E391" s="3">
@@ -8990,7 +8993,7 @@
       <c r="C392" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D392" s="2">
+      <c r="D392" s="19">
         <v>313.5</v>
       </c>
       <c r="E392" s="3">
@@ -9011,7 +9014,7 @@
       <c r="C393" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D393" s="2">
+      <c r="D393" s="19">
         <v>614.5</v>
       </c>
       <c r="E393" s="3">
@@ -9032,7 +9035,7 @@
       <c r="C394" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="D394" s="2">
+      <c r="D394" s="19">
         <v>499.5</v>
       </c>
       <c r="E394" s="3">
@@ -9053,7 +9056,7 @@
       <c r="C395" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D395" s="2">
+      <c r="D395" s="19">
         <v>2161.5</v>
       </c>
       <c r="E395" s="3">
@@ -9074,7 +9077,7 @@
       <c r="C396" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D396" s="2">
+      <c r="D396" s="19">
         <v>2420.5</v>
       </c>
       <c r="E396" s="3">
@@ -9095,7 +9098,7 @@
       <c r="C397" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D397" s="2">
+      <c r="D397" s="19">
         <v>549</v>
       </c>
       <c r="E397" s="3">
@@ -9116,7 +9119,7 @@
       <c r="C398" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D398" s="2">
+      <c r="D398" s="19">
         <v>2047</v>
       </c>
       <c r="E398" s="3">
@@ -9137,7 +9140,7 @@
       <c r="C399" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D399" s="2">
+      <c r="D399" s="19">
         <v>1301.5</v>
       </c>
       <c r="E399" s="3">
@@ -9158,7 +9161,7 @@
       <c r="C400" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D400" s="2">
+      <c r="D400" s="19">
         <v>1043.5</v>
       </c>
       <c r="E400" s="3">
@@ -9179,7 +9182,7 @@
       <c r="C401" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D401" s="2">
+      <c r="D401" s="19">
         <v>1644</v>
       </c>
       <c r="E401" s="3">
@@ -9200,7 +9203,7 @@
       <c r="C402" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D402" s="2">
+      <c r="D402" s="19">
         <v>344</v>
       </c>
       <c r="E402" s="3">
@@ -9221,7 +9224,7 @@
       <c r="C403" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D403" s="2">
+      <c r="D403" s="19">
         <v>760.5</v>
       </c>
       <c r="E403" s="3">
@@ -9242,7 +9245,7 @@
       <c r="C404" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="D404" s="2">
+      <c r="D404" s="19">
         <v>533</v>
       </c>
       <c r="E404" s="3">
@@ -9263,7 +9266,7 @@
       <c r="C405" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D405" s="2">
+      <c r="D405" s="19">
         <v>2255.5</v>
       </c>
       <c r="E405" s="3">
@@ -9284,7 +9287,7 @@
       <c r="C406" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D406" s="2">
+      <c r="D406" s="19">
         <v>2323</v>
       </c>
       <c r="E406" s="3">
@@ -9305,7 +9308,7 @@
       <c r="C407" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D407" s="2">
+      <c r="D407" s="19">
         <v>681.5</v>
       </c>
       <c r="E407" s="3">
@@ -9326,7 +9329,7 @@
       <c r="C408" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D408" s="2">
+      <c r="D408" s="19">
         <v>2170</v>
       </c>
       <c r="E408" s="3">
@@ -9347,7 +9350,7 @@
       <c r="C409" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D409" s="2">
+      <c r="D409" s="19">
         <v>1371</v>
       </c>
       <c r="E409" s="3">
@@ -9368,7 +9371,7 @@
       <c r="C410" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D410" s="2">
+      <c r="D410" s="19">
         <v>1171.5</v>
       </c>
       <c r="E410" s="3">
@@ -9389,7 +9392,7 @@
       <c r="C411" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D411" s="2">
+      <c r="D411" s="19">
         <v>1809</v>
       </c>
       <c r="E411" s="3">
@@ -9410,7 +9413,7 @@
       <c r="C412" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D412" s="2">
+      <c r="D412" s="19">
         <v>269</v>
       </c>
       <c r="E412" s="3">
@@ -9431,7 +9434,7 @@
       <c r="C413" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D413" s="2">
+      <c r="D413" s="19">
         <v>803.5</v>
       </c>
       <c r="E413" s="3">
@@ -9452,7 +9455,7 @@
       <c r="C414" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="D414" s="2">
+      <c r="D414" s="19">
         <v>576.5</v>
       </c>
       <c r="E414" s="3">
@@ -9473,7 +9476,7 @@
       <c r="C415" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D415" s="2">
+      <c r="D415" s="19">
         <v>2406</v>
       </c>
       <c r="E415" s="3">
@@ -9494,7 +9497,7 @@
       <c r="C416" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D416" s="2">
+      <c r="D416" s="19">
         <v>4554</v>
       </c>
       <c r="E416" s="3">
@@ -9515,7 +9518,7 @@
       <c r="C417" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D417" s="2">
+      <c r="D417" s="19">
         <v>729</v>
       </c>
       <c r="E417" s="3">
@@ -9536,7 +9539,7 @@
       <c r="C418" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D418" s="2">
+      <c r="D418" s="19">
         <v>2227.5</v>
       </c>
       <c r="E418" s="3">
@@ -9557,7 +9560,7 @@
       <c r="C419" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D419" s="2">
+      <c r="D419" s="19">
         <v>1580.5</v>
       </c>
       <c r="E419" s="3">
@@ -9578,7 +9581,7 @@
       <c r="C420" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D420" s="2">
+      <c r="D420" s="19">
         <v>1282</v>
       </c>
       <c r="E420" s="3">
@@ -9599,7 +9602,7 @@
       <c r="C421" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D421" s="2">
+      <c r="D421" s="19">
         <v>1913.5</v>
       </c>
       <c r="E421" s="3">
@@ -9620,7 +9623,7 @@
       <c r="C422" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D422" s="2">
+      <c r="D422" s="19">
         <v>426.5</v>
       </c>
       <c r="E422" s="3">
@@ -9641,7 +9644,7 @@
       <c r="C423" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D423" s="2">
+      <c r="D423" s="19">
         <v>869.5</v>
       </c>
       <c r="E423" s="3">
@@ -9662,7 +9665,7 @@
       <c r="C424" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="D424" s="2">
+      <c r="D424" s="19">
         <v>693.5</v>
       </c>
       <c r="E424" s="3">
@@ -9683,7 +9686,7 @@
       <c r="C425" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D425" s="2">
+      <c r="D425" s="19">
         <v>2439</v>
       </c>
       <c r="E425" s="3">
@@ -9704,7 +9707,7 @@
       <c r="C426" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D426" s="2">
+      <c r="D426" s="19">
         <v>2607.5</v>
       </c>
       <c r="E426" s="3">
@@ -9725,7 +9728,7 @@
       <c r="C427" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D427" s="2">
+      <c r="D427" s="19">
         <v>747.5</v>
       </c>
       <c r="E427" s="3">
@@ -9746,7 +9749,7 @@
       <c r="C428" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D428" s="2">
+      <c r="D428" s="19">
         <v>2270.5</v>
       </c>
       <c r="E428" s="3">
@@ -9767,7 +9770,7 @@
       <c r="C429" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D429" s="2">
+      <c r="D429" s="19">
         <v>1621</v>
       </c>
       <c r="E429" s="3">
@@ -9788,7 +9791,7 @@
       <c r="C430" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D430" s="2">
+      <c r="D430" s="19">
         <v>1354</v>
       </c>
       <c r="E430" s="3">
@@ -9809,7 +9812,7 @@
       <c r="C431" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D431" s="2">
+      <c r="D431" s="19">
         <v>1921.5</v>
       </c>
       <c r="E431" s="3">
@@ -9830,7 +9833,7 @@
       <c r="C432" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D432" s="2">
+      <c r="D432" s="19">
         <v>426.5</v>
       </c>
       <c r="E432" s="3">
@@ -9851,7 +9854,7 @@
       <c r="C433" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D433" s="2">
+      <c r="D433" s="19">
         <v>917.5</v>
       </c>
       <c r="E433" s="3">
@@ -9872,7 +9875,7 @@
       <c r="C434" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="D434" s="2">
+      <c r="D434" s="19">
         <v>693.5</v>
       </c>
       <c r="E434" s="3">
@@ -9893,7 +9896,7 @@
       <c r="C435" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D435" s="2">
+      <c r="D435" s="19">
         <v>2489.5</v>
       </c>
       <c r="E435" s="3">
@@ -9914,7 +9917,7 @@
       <c r="C436" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D436" s="2">
+      <c r="D436" s="19">
         <v>2852</v>
       </c>
       <c r="E436" s="3">
@@ -9935,7 +9938,7 @@
       <c r="C437" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D437" s="2">
+      <c r="D437" s="19">
         <v>783.5</v>
       </c>
       <c r="E437" s="3">
@@ -9956,7 +9959,7 @@
       <c r="C438" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D438" s="2">
+      <c r="D438" s="19">
         <v>2437</v>
       </c>
       <c r="E438" s="3">
@@ -9977,7 +9980,7 @@
       <c r="C439" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D439" s="2">
+      <c r="D439" s="19">
         <v>1722.5</v>
       </c>
       <c r="E439" s="3">
@@ -9998,7 +10001,7 @@
       <c r="C440" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D440" s="2">
+      <c r="D440" s="19">
         <v>1442.5</v>
       </c>
       <c r="E440" s="3">
@@ -10019,7 +10022,7 @@
       <c r="C441" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D441" s="2">
+      <c r="D441" s="19">
         <v>2041.5</v>
       </c>
       <c r="E441" s="3">
@@ -10040,7 +10043,7 @@
       <c r="C442" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D442" s="2">
+      <c r="D442" s="19">
         <v>466.5</v>
       </c>
       <c r="E442" s="3">
@@ -10061,7 +10064,7 @@
       <c r="C443" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D443" s="2">
+      <c r="D443" s="19">
         <v>1056.5</v>
       </c>
       <c r="E443" s="3">
@@ -10082,7 +10085,7 @@
       <c r="C444" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="D444" s="2">
+      <c r="D444" s="19">
         <v>709.5</v>
       </c>
       <c r="E444" s="3">
@@ -10103,7 +10106,7 @@
       <c r="C445" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D445" s="2">
+      <c r="D445" s="19">
         <v>2599</v>
       </c>
       <c r="E445" s="3">
@@ -10124,7 +10127,7 @@
       <c r="C446" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D446" s="2">
+      <c r="D446" s="19">
         <v>2923.5</v>
       </c>
       <c r="E446" s="3">
@@ -10145,7 +10148,7 @@
       <c r="C447" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D447" s="2">
+      <c r="D447" s="19">
         <v>797</v>
       </c>
       <c r="E447" s="3">
@@ -10166,7 +10169,7 @@
       <c r="C448" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D448" s="2">
+      <c r="D448" s="19">
         <v>2543.5</v>
       </c>
       <c r="E448" s="3">
@@ -10187,7 +10190,7 @@
       <c r="C449" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D449" s="2">
+      <c r="D449" s="19">
         <v>1840.5</v>
       </c>
       <c r="E449" s="3">
@@ -10208,7 +10211,7 @@
       <c r="C450" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D450" s="2">
+      <c r="D450" s="19">
         <v>1531.5</v>
       </c>
       <c r="E450" s="3">
@@ -10229,7 +10232,7 @@
       <c r="C451" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D451" s="2">
+      <c r="D451" s="19">
         <v>2213.5</v>
       </c>
       <c r="E451" s="3">
@@ -10250,7 +10253,7 @@
       <c r="C452" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D452" s="2">
+      <c r="D452" s="19">
         <v>528</v>
       </c>
       <c r="E452" s="3">
@@ -10271,7 +10274,7 @@
       <c r="C453" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D453" s="2">
+      <c r="D453" s="19">
         <v>1146.5</v>
       </c>
       <c r="E453" s="3">
@@ -10292,7 +10295,7 @@
       <c r="C454" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="D454" s="2">
+      <c r="D454" s="19">
         <v>709.5</v>
       </c>
       <c r="E454" s="3">
@@ -10313,7 +10316,7 @@
       <c r="C455" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D455" s="2">
+      <c r="D455" s="19">
         <v>2752.5</v>
       </c>
       <c r="E455" s="3">
@@ -10334,7 +10337,7 @@
       <c r="C456" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D456" s="2">
+      <c r="D456" s="19">
         <v>3009</v>
       </c>
       <c r="E456" s="3">
@@ -10355,7 +10358,7 @@
       <c r="C457" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D457" s="2">
+      <c r="D457" s="19">
         <v>850.5</v>
       </c>
       <c r="E457" s="3">
@@ -10376,7 +10379,7 @@
       <c r="C458" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D458" s="2">
+      <c r="D458" s="19">
         <v>2663</v>
       </c>
       <c r="E458" s="3">
@@ -10397,7 +10400,7 @@
       <c r="C459" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D459" s="2">
+      <c r="D459" s="19">
         <v>2075.5</v>
       </c>
       <c r="E459" s="3">
@@ -10418,7 +10421,7 @@
       <c r="C460" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D460" s="2">
+      <c r="D460" s="19">
         <v>1586.5</v>
       </c>
       <c r="E460" s="3">
@@ -10439,7 +10442,7 @@
       <c r="C461" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D461" s="2">
+      <c r="D461" s="19">
         <v>2342</v>
       </c>
       <c r="E461" s="3">
@@ -10460,7 +10463,7 @@
       <c r="C462" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D462" s="2">
+      <c r="D462" s="19">
         <v>592</v>
       </c>
       <c r="E462" s="3">
@@ -10481,7 +10484,7 @@
       <c r="C463" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D463" s="2">
+      <c r="D463" s="19">
         <v>1170</v>
       </c>
       <c r="E463" s="3">
@@ -10502,7 +10505,7 @@
       <c r="C464" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="D464" s="2">
+      <c r="D464" s="19">
         <v>743.5</v>
       </c>
       <c r="E464" s="3">
@@ -10523,7 +10526,7 @@
       <c r="C465" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D465" s="2">
+      <c r="D465" s="19">
         <v>3046.5</v>
       </c>
       <c r="E465" s="3">
@@ -10544,7 +10547,7 @@
       <c r="C466" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D466" s="2">
+      <c r="D466" s="19">
         <v>3102.5</v>
       </c>
       <c r="E466" s="3">
@@ -10565,7 +10568,7 @@
       <c r="C467" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D467" s="2">
+      <c r="D467" s="19">
         <v>904</v>
       </c>
       <c r="E467" s="3">
@@ -10586,7 +10589,7 @@
       <c r="C468" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D468" s="2">
+      <c r="D468" s="19">
         <v>2787</v>
       </c>
       <c r="E468" s="3">
@@ -10607,7 +10610,7 @@
       <c r="C469" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D469" s="2">
+      <c r="D469" s="19">
         <v>2203.5</v>
       </c>
       <c r="E469" s="3">
@@ -10628,7 +10631,7 @@
       <c r="C470" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D470" s="2">
+      <c r="D470" s="19">
         <v>1725.5</v>
       </c>
       <c r="E470" s="3">
@@ -10649,7 +10652,7 @@
       <c r="C471" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D471" s="2">
+      <c r="D471" s="19">
         <v>2442.5</v>
       </c>
       <c r="E471" s="3">
@@ -10670,7 +10673,7 @@
       <c r="C472" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D472" s="2">
+      <c r="D472" s="19">
         <v>656</v>
       </c>
       <c r="E472" s="3">
@@ -10691,7 +10694,7 @@
       <c r="C473" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D473" s="2">
+      <c r="D473" s="19">
         <v>1302.5</v>
       </c>
       <c r="E473" s="3">
@@ -10712,7 +10715,7 @@
       <c r="C474" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="D474" s="2">
+      <c r="D474" s="19">
         <v>790.5</v>
       </c>
       <c r="E474" s="3">
@@ -10733,7 +10736,9 @@
       <c r="C475" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D475" s="2"/>
+      <c r="D475" s="19">
+        <v>3105</v>
+      </c>
       <c r="E475" s="3">
         <v>4477.5</v>
       </c>
@@ -10752,7 +10757,9 @@
       <c r="C476" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D476" s="2"/>
+      <c r="D476" s="19">
+        <v>3468</v>
+      </c>
       <c r="E476" s="3">
         <v>3980</v>
       </c>
@@ -10771,7 +10778,9 @@
       <c r="C477" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D477" s="2"/>
+      <c r="D477" s="19">
+        <v>946</v>
+      </c>
       <c r="E477" s="3">
         <v>1492.5</v>
       </c>
@@ -10790,7 +10799,9 @@
       <c r="C478" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D478" s="2"/>
+      <c r="D478" s="19">
+        <v>2922.5</v>
+      </c>
       <c r="E478" s="3">
         <v>4170</v>
       </c>
@@ -10809,7 +10820,9 @@
       <c r="C479" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D479" s="2"/>
+      <c r="D479" s="19">
+        <v>2366</v>
+      </c>
       <c r="E479" s="3">
         <v>2780</v>
       </c>
@@ -10828,7 +10841,9 @@
       <c r="C480" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D480" s="2"/>
+      <c r="D480" s="19">
+        <v>1888</v>
+      </c>
       <c r="E480" s="3">
         <v>1710</v>
       </c>
@@ -10847,7 +10862,9 @@
       <c r="C481" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D481" s="2"/>
+      <c r="D481" s="19">
+        <v>2514.5</v>
+      </c>
       <c r="E481" s="3">
         <v>1610</v>
       </c>
@@ -10866,7 +10883,9 @@
       <c r="C482" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D482" s="2"/>
+      <c r="D482" s="19">
+        <v>781.5</v>
+      </c>
       <c r="E482" s="3">
         <v>1120</v>
       </c>
@@ -10885,7 +10904,9 @@
       <c r="C483" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D483" s="2"/>
+      <c r="D483" s="19">
+        <v>1417.5</v>
+      </c>
       <c r="E483" s="3">
         <v>1405</v>
       </c>
@@ -10904,7 +10925,9 @@
       <c r="C484" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="D484" s="2"/>
+      <c r="D484" s="19">
+        <v>852</v>
+      </c>
       <c r="E484" s="3">
         <v>1000</v>
       </c>
@@ -10923,7 +10946,9 @@
       <c r="C485" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D485" s="2"/>
+      <c r="D485" s="19">
+        <v>3105</v>
+      </c>
       <c r="E485" s="3">
         <v>4477.5</v>
       </c>
@@ -10942,7 +10967,9 @@
       <c r="C486" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D486" s="2"/>
+      <c r="D486" s="19">
+        <v>3512</v>
+      </c>
       <c r="E486" s="3">
         <v>3980</v>
       </c>
@@ -10961,7 +10988,9 @@
       <c r="C487" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D487" s="2"/>
+      <c r="D487" s="19">
+        <v>1023.5</v>
+      </c>
       <c r="E487" s="3">
         <v>1492.5</v>
       </c>
@@ -10980,7 +11009,9 @@
       <c r="C488" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D488" s="2"/>
+      <c r="D488" s="19">
+        <v>2991.5</v>
+      </c>
       <c r="E488" s="3">
         <v>4170</v>
       </c>
@@ -10999,7 +11030,9 @@
       <c r="C489" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D489" s="2"/>
+      <c r="D489" s="19">
+        <v>2450.5</v>
+      </c>
       <c r="E489" s="3">
         <v>2780</v>
       </c>
@@ -11018,7 +11051,9 @@
       <c r="C490" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D490" s="2"/>
+      <c r="D490" s="19">
+        <v>1888</v>
+      </c>
       <c r="E490" s="3">
         <v>1710</v>
       </c>
@@ -11037,7 +11072,9 @@
       <c r="C491" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D491" s="2"/>
+      <c r="D491" s="19">
+        <v>2535.5</v>
+      </c>
       <c r="E491" s="3">
         <v>1610</v>
       </c>
@@ -11056,7 +11093,9 @@
       <c r="C492" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D492" s="2"/>
+      <c r="D492" s="19">
+        <v>781.5</v>
+      </c>
       <c r="E492" s="3">
         <v>1120</v>
       </c>
@@ -11075,7 +11114,9 @@
       <c r="C493" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D493" s="2"/>
+      <c r="D493" s="19">
+        <v>1461.5</v>
+      </c>
       <c r="E493" s="3">
         <v>1405</v>
       </c>
@@ -11094,7 +11135,9 @@
       <c r="C494" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="D494" s="2"/>
+      <c r="D494" s="19">
+        <v>868</v>
+      </c>
       <c r="E494" s="3">
         <v>1000</v>
       </c>
@@ -11113,7 +11156,7 @@
       <c r="C495" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D495" s="2"/>
+      <c r="D495" s="19"/>
       <c r="E495" s="3">
         <v>4477.5</v>
       </c>
@@ -11131,7 +11174,7 @@
       <c r="C496" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D496" s="2"/>
+      <c r="D496" s="19"/>
       <c r="E496" s="3">
         <v>3980</v>
       </c>
@@ -11149,7 +11192,7 @@
       <c r="C497" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D497" s="2"/>
+      <c r="D497" s="19"/>
       <c r="E497" s="3">
         <v>1492.5</v>
       </c>
@@ -11167,7 +11210,7 @@
       <c r="C498" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D498" s="2"/>
+      <c r="D498" s="19"/>
       <c r="E498" s="3">
         <v>4170</v>
       </c>
@@ -11185,7 +11228,7 @@
       <c r="C499" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D499" s="2"/>
+      <c r="D499" s="19"/>
       <c r="E499" s="3">
         <v>2780</v>
       </c>
@@ -11203,7 +11246,7 @@
       <c r="C500" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D500" s="2"/>
+      <c r="D500" s="19"/>
       <c r="E500" s="3">
         <v>1710</v>
       </c>
@@ -11221,7 +11264,7 @@
       <c r="C501" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D501" s="2"/>
+      <c r="D501" s="19"/>
       <c r="E501" s="3">
         <v>1610</v>
       </c>
@@ -11239,7 +11282,7 @@
       <c r="C502" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D502" s="2"/>
+      <c r="D502" s="19"/>
       <c r="E502" s="3">
         <v>1120</v>
       </c>
@@ -11257,7 +11300,7 @@
       <c r="C503" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D503" s="2"/>
+      <c r="D503" s="19"/>
       <c r="E503" s="3">
         <v>1405</v>
       </c>
@@ -11275,7 +11318,7 @@
       <c r="C504" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="D504" s="2"/>
+      <c r="D504" s="19"/>
       <c r="E504" s="3">
         <v>1000</v>
       </c>
@@ -17491,7 +17534,7 @@
         <v>2</v>
       </c>
       <c r="AD14" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE14" s="8"/>
       <c r="AF14" s="8"/>
@@ -17653,7 +17696,7 @@
         <v>1</v>
       </c>
       <c r="AD16" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE16" s="8"/>
       <c r="AF16" s="8"/>
@@ -17815,7 +17858,7 @@
         <v>1</v>
       </c>
       <c r="AD18" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE18" s="8"/>
       <c r="AF18" s="8"/>
@@ -17977,7 +18020,7 @@
         <v>1</v>
       </c>
       <c r="AD20" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE20" s="8"/>
       <c r="AF20" s="8"/>

--- a/dados.xlsx
+++ b/dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://concresupersc-my.sharepoint.com/personal/marketing_concresupersc_onmicrosoft_com/Documents/Área de Trabalho/C.I.V/Dashbord/DASHBOARD-METAS-PROPOSTAS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="886" documentId="8_{A291900F-2FC4-4CBC-95EF-8FF0E06A2678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1DF304ED-88B0-4B70-AE0D-B058164CC6B6}"/>
+  <xr:revisionPtr revIDLastSave="904" documentId="8_{A291900F-2FC4-4CBC-95EF-8FF0E06A2678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5C32C9E3-7EBC-4EBF-8184-DE6579C46365}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-3255" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -11833,7 +11833,9 @@
       <c r="C525" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D525" s="2"/>
+      <c r="D525" s="2">
+        <v>407.5</v>
+      </c>
       <c r="E525" s="18">
         <v>4252.5</v>
       </c>
@@ -11851,7 +11853,9 @@
       <c r="C526" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D526" s="2"/>
+      <c r="D526" s="6">
+        <v>478</v>
+      </c>
       <c r="E526" s="18">
         <v>3780</v>
       </c>
@@ -11869,7 +11873,9 @@
       <c r="C527" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D527" s="2"/>
+      <c r="D527" s="2">
+        <v>346.5</v>
+      </c>
       <c r="E527" s="18">
         <v>1417.5</v>
       </c>
@@ -11887,7 +11893,9 @@
       <c r="C528" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D528" s="2"/>
+      <c r="D528" s="2">
+        <v>320</v>
+      </c>
       <c r="E528" s="18">
         <v>3900</v>
       </c>
@@ -11905,7 +11913,9 @@
       <c r="C529" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D529" s="2"/>
+      <c r="D529" s="2">
+        <v>201.5</v>
+      </c>
       <c r="E529" s="18">
         <v>2600</v>
       </c>
@@ -11923,7 +11933,9 @@
       <c r="C530" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D530" s="2"/>
+      <c r="D530" s="2">
+        <v>319</v>
+      </c>
       <c r="E530" s="18">
         <v>1670</v>
       </c>
@@ -11941,7 +11953,9 @@
       <c r="C531" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D531" s="2"/>
+      <c r="D531" s="2">
+        <v>255.5</v>
+      </c>
       <c r="E531" s="18">
         <v>1610</v>
       </c>
@@ -11959,7 +11973,9 @@
       <c r="C532" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D532" s="2"/>
+      <c r="D532" s="2">
+        <v>117.5</v>
+      </c>
       <c r="E532" s="18">
         <v>1150</v>
       </c>
@@ -11977,7 +11993,9 @@
       <c r="C533" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D533" s="2"/>
+      <c r="D533" s="2">
+        <v>250.5</v>
+      </c>
       <c r="E533" s="18">
         <v>1405</v>
       </c>
@@ -11995,7 +12013,9 @@
       <c r="C534" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="D534" s="2"/>
+      <c r="D534" s="2">
+        <v>92</v>
+      </c>
       <c r="E534" s="18">
         <v>1200</v>
       </c>
@@ -16909,7 +16929,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <sheetPr filterMode="1">
+  <sheetPr>
     <tabColor rgb="FF375623"/>
   </sheetPr>
   <dimension ref="A1:H61"/>
@@ -16935,7 +16955,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>17</v>
       </c>
@@ -16949,7 +16969,7 @@
         <v>4284</v>
       </c>
     </row>
-    <row r="3" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="9" t="s">
         <v>18</v>
       </c>
@@ -16978,7 +16998,7 @@
         <v>4252.5</v>
       </c>
     </row>
-    <row r="5" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
         <v>20</v>
       </c>
@@ -16990,7 +17010,7 @@
       </c>
       <c r="D5" s="17"/>
     </row>
-    <row r="6" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>21</v>
       </c>
@@ -17002,7 +17022,7 @@
       </c>
       <c r="D6" s="18"/>
     </row>
-    <row r="7" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
         <v>22</v>
       </c>
@@ -17014,7 +17034,7 @@
       </c>
       <c r="D7" s="17"/>
     </row>
-    <row r="8" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
         <v>17</v>
       </c>
@@ -17028,7 +17048,7 @@
         <v>3808</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
         <v>18</v>
       </c>
@@ -17056,7 +17076,7 @@
         <v>3780</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
         <v>20</v>
       </c>
@@ -17068,7 +17088,7 @@
       </c>
       <c r="D11" s="17"/>
     </row>
-    <row r="12" spans="1:8" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
         <v>21</v>
       </c>
@@ -17080,7 +17100,7 @@
       </c>
       <c r="D12" s="18"/>
     </row>
-    <row r="13" spans="1:8" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
         <v>22</v>
       </c>
@@ -17092,7 +17112,7 @@
       </c>
       <c r="D13" s="17"/>
     </row>
-    <row r="14" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
         <v>17</v>
       </c>
@@ -17106,7 +17126,7 @@
         <v>1428</v>
       </c>
     </row>
-    <row r="15" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
         <v>18</v>
       </c>
@@ -17134,7 +17154,7 @@
         <v>1417.5</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
         <v>20</v>
       </c>
@@ -17146,7 +17166,7 @@
       </c>
       <c r="D17" s="17"/>
     </row>
-    <row r="18" spans="1:4" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
         <v>21</v>
       </c>
@@ -17158,7 +17178,7 @@
       </c>
       <c r="D18" s="18"/>
     </row>
-    <row r="19" spans="1:4" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="9" t="s">
         <v>22</v>
       </c>
@@ -17170,7 +17190,7 @@
       </c>
       <c r="D19" s="17"/>
     </row>
-    <row r="20" spans="1:4" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
         <v>17</v>
       </c>
@@ -17184,7 +17204,7 @@
         <v>4290</v>
       </c>
     </row>
-    <row r="21" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="9" t="s">
         <v>18</v>
       </c>
@@ -17212,7 +17232,7 @@
         <v>3900</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="9" t="s">
         <v>20</v>
       </c>
@@ -17224,7 +17244,7 @@
       </c>
       <c r="D23" s="17"/>
     </row>
-    <row r="24" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="8" t="s">
         <v>21</v>
       </c>
@@ -17236,7 +17256,7 @@
       </c>
       <c r="D24" s="18"/>
     </row>
-    <row r="25" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="9" t="s">
         <v>22</v>
       </c>
@@ -17248,7 +17268,7 @@
       </c>
       <c r="D25" s="17"/>
     </row>
-    <row r="26" spans="1:4" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
         <v>17</v>
       </c>
@@ -17262,7 +17282,7 @@
         <v>2860</v>
       </c>
     </row>
-    <row r="27" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="9" t="s">
         <v>18</v>
       </c>
@@ -17290,7 +17310,7 @@
         <v>2600</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="9" t="s">
         <v>20</v>
       </c>
@@ -17302,7 +17322,7 @@
       </c>
       <c r="D29" s="17"/>
     </row>
-    <row r="30" spans="1:4" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="8" t="s">
         <v>21</v>
       </c>
@@ -17314,7 +17334,7 @@
       </c>
       <c r="D30" s="18"/>
     </row>
-    <row r="31" spans="1:4" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="9" t="s">
         <v>22</v>
       </c>
@@ -17326,7 +17346,7 @@
       </c>
       <c r="D31" s="17"/>
     </row>
-    <row r="32" spans="1:4" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="8" t="s">
         <v>17</v>
       </c>
@@ -17340,7 +17360,7 @@
         <v>1710</v>
       </c>
     </row>
-    <row r="33" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="9" t="s">
         <v>18</v>
       </c>
@@ -17368,7 +17388,7 @@
         <v>1670</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="9" t="s">
         <v>20</v>
       </c>
@@ -17380,7 +17400,7 @@
       </c>
       <c r="D35" s="17"/>
     </row>
-    <row r="36" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="8" t="s">
         <v>21</v>
       </c>
@@ -17392,7 +17412,7 @@
       </c>
       <c r="D36" s="18"/>
     </row>
-    <row r="37" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="9" t="s">
         <v>22</v>
       </c>
@@ -17404,7 +17424,7 @@
       </c>
       <c r="D37" s="17"/>
     </row>
-    <row r="38" spans="1:4" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="8" t="s">
         <v>17</v>
       </c>
@@ -17418,7 +17438,7 @@
         <v>1710</v>
       </c>
     </row>
-    <row r="39" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="9" t="s">
         <v>18</v>
       </c>
@@ -17446,7 +17466,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="41" spans="1:4" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="9" t="s">
         <v>20</v>
       </c>
@@ -17458,7 +17478,7 @@
       </c>
       <c r="D41" s="17"/>
     </row>
-    <row r="42" spans="1:4" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="8" t="s">
         <v>21</v>
       </c>
@@ -17470,7 +17490,7 @@
       </c>
       <c r="D42" s="18"/>
     </row>
-    <row r="43" spans="1:4" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="9" t="s">
         <v>22</v>
       </c>
@@ -17482,7 +17502,7 @@
       </c>
       <c r="D43" s="17"/>
     </row>
-    <row r="44" spans="1:4" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="8" t="s">
         <v>17</v>
       </c>
@@ -17496,7 +17516,7 @@
         <v>1160</v>
       </c>
     </row>
-    <row r="45" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="9" t="s">
         <v>18</v>
       </c>
@@ -17524,7 +17544,7 @@
         <v>1150</v>
       </c>
     </row>
-    <row r="47" spans="1:4" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="9" t="s">
         <v>20</v>
       </c>
@@ -17536,7 +17556,7 @@
       </c>
       <c r="D47" s="17"/>
     </row>
-    <row r="48" spans="1:4" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="8" t="s">
         <v>21</v>
       </c>
@@ -17548,7 +17568,7 @@
       </c>
       <c r="D48" s="18"/>
     </row>
-    <row r="49" spans="1:4" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="9" t="s">
         <v>22</v>
       </c>
@@ -17560,7 +17580,7 @@
       </c>
       <c r="D49" s="17"/>
     </row>
-    <row r="50" spans="1:4" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="8" t="s">
         <v>17</v>
       </c>
@@ -17574,7 +17594,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="51" spans="1:4" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="9" t="s">
         <v>18</v>
       </c>
@@ -17602,7 +17622,7 @@
         <v>1405</v>
       </c>
     </row>
-    <row r="53" spans="1:4" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="9" t="s">
         <v>20</v>
       </c>
@@ -17614,7 +17634,7 @@
       </c>
       <c r="D53" s="17"/>
     </row>
-    <row r="54" spans="1:4" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="8" t="s">
         <v>21</v>
       </c>
@@ -17626,7 +17646,7 @@
       </c>
       <c r="D54" s="18"/>
     </row>
-    <row r="55" spans="1:4" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="9" t="s">
         <v>22</v>
       </c>
@@ -17638,7 +17658,7 @@
       </c>
       <c r="D55" s="17"/>
     </row>
-    <row r="56" spans="1:4" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="8" t="s">
         <v>17</v>
       </c>
@@ -17652,7 +17672,7 @@
         <v>2100</v>
       </c>
     </row>
-    <row r="57" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="9" t="s">
         <v>18</v>
       </c>
@@ -17680,7 +17700,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="59" spans="1:4" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="9" t="s">
         <v>20</v>
       </c>
@@ -17692,7 +17712,7 @@
       </c>
       <c r="D59" s="17"/>
     </row>
-    <row r="60" spans="1:4" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="8" t="s">
         <v>21</v>
       </c>
@@ -17704,7 +17724,7 @@
       </c>
       <c r="D60" s="18"/>
     </row>
-    <row r="61" spans="1:4" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="9" t="s">
         <v>22</v>
       </c>
@@ -17717,13 +17737,7 @@
       <c r="D61" s="17"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D61" xr:uid="{00000000-0001-0000-0100-000000000000}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="Setembro"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:D61" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
@@ -17731,7 +17745,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <sheetPr>
+  <sheetPr filterMode="1">
     <tabColor rgb="FF2E75B6"/>
   </sheetPr>
   <dimension ref="A1:AG34"/>
@@ -17844,7 +17858,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>17</v>
       </c>
@@ -17945,7 +17959,7 @@
         <v>46234</v>
       </c>
     </row>
-    <row r="3" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
         <v>17</v>
       </c>
@@ -18030,7 +18044,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>17</v>
       </c>
@@ -18115,7 +18129,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
         <v>17</v>
       </c>
@@ -18200,7 +18214,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>17</v>
       </c>
@@ -18285,7 +18299,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
         <v>17</v>
       </c>
@@ -18370,7 +18384,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
         <v>17</v>
       </c>
@@ -18455,7 +18469,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
         <v>17</v>
       </c>
@@ -18540,7 +18554,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
         <v>17</v>
       </c>
@@ -18625,7 +18639,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
         <v>17</v>
       </c>
@@ -18710,7 +18724,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
         <v>17</v>
       </c>
@@ -18795,7 +18809,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
         <v>18</v>
       </c>
@@ -18896,7 +18910,7 @@
         <v>46265</v>
       </c>
     </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
         <v>18</v>
       </c>
@@ -18977,7 +18991,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
         <v>18</v>
       </c>
@@ -19058,7 +19072,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
         <v>18</v>
       </c>
@@ -19139,7 +19153,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
         <v>18</v>
       </c>
@@ -19220,7 +19234,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
         <v>18</v>
       </c>
@@ -19301,7 +19315,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="9" t="s">
         <v>18</v>
       </c>
@@ -19382,7 +19396,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
         <v>18</v>
       </c>
@@ -19463,7 +19477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="9" t="s">
         <v>18</v>
       </c>
@@ -19544,7 +19558,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="8" t="s">
         <v>18</v>
       </c>
@@ -19625,7 +19639,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:33" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="9" t="s">
         <v>18</v>
       </c>
@@ -19901,7 +19915,7 @@
         <v>0</v>
       </c>
       <c r="E26" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F26" s="8">
         <v>0</v>
@@ -20065,7 +20079,7 @@
         <v>1</v>
       </c>
       <c r="E28" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F28" s="8">
         <v>0</v>
@@ -20147,7 +20161,7 @@
         <v>1</v>
       </c>
       <c r="E29" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F29" s="8">
         <v>0</v>
@@ -20626,7 +20640,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:A34" xr:uid="{00000000-0001-0000-0200-000000000000}"/>
+  <autoFilter ref="A1:A34" xr:uid="{00000000-0001-0000-0200-000000000000}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="Setembro"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>